--- a/src/test/resources/TestDriver/TestRevenue_DSL/Test.xlsx
+++ b/src/test/resources/TestDriver/TestRevenue_DSL/Test.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="17"/>
   </bookViews>
   <sheets>
     <sheet name="Test" sheetId="1" state="visible" r:id="rId1"/>
@@ -42,7 +42,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">O_TransactionActivity5!$A$2:$J$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">O_Attribute5!$A$2:$G$46</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">O_Instrument5!$A$2:$F$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">O_InstrumentAttribute!$A$2:$Q$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">O_InstrumentAttribute!$A$2:$Q$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">O_TransactionActivity!$A$2:$J$18</definedName>
   </definedNames>
   <calcPr/>
@@ -574,11 +574,10 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="31">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyProtection="1"/>
     <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyProtection="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyProtection="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
@@ -1093,7 +1092,7 @@
       </c>
     </row>
     <row r="6" ht="12.75" customHeight="1">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
@@ -1132,7 +1131,7 @@
       <c r="B9" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="4">
+      <c r="C9" s="3">
         <v>44592</v>
       </c>
     </row>
@@ -1154,7 +1153,7 @@
       <c r="B11" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C11" s="4">
+      <c r="C11" s="3">
         <v>44620</v>
       </c>
     </row>
@@ -1165,7 +1164,7 @@
       <c r="B12" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="4">
+      <c r="C12" s="3">
         <v>44651</v>
       </c>
     </row>
@@ -1187,7 +1186,7 @@
       <c r="B14" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C14" s="4">
+      <c r="C14" s="3">
         <v>44681</v>
       </c>
     </row>
@@ -1209,7 +1208,7 @@
       <c r="B16" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C16" s="4">
+      <c r="C16" s="3">
         <v>44712</v>
       </c>
     </row>
@@ -1236,10 +1235,10 @@
   </cols>
   <sheetData>
     <row r="1" ht="15">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>25</v>
       </c>
     </row>
@@ -1273,13 +1272,13 @@
       <c r="C3" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D3" s="16">
+      <c r="D3" s="15">
         <v>-9.9999999996214228e-05</v>
       </c>
-      <c r="E3" s="16">
-        <v>0</v>
-      </c>
-      <c r="F3" s="16">
+      <c r="E3" s="15">
+        <v>0</v>
+      </c>
+      <c r="F3" s="15">
         <v>-9.9999999996214228e-05</v>
       </c>
     </row>
@@ -1293,13 +1292,13 @@
       <c r="C4" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D4" s="16">
+      <c r="D4" s="15">
         <v>-342.81810000000002</v>
       </c>
-      <c r="E4" s="16">
-        <v>0</v>
-      </c>
-      <c r="F4" s="16">
+      <c r="E4" s="15">
+        <v>0</v>
+      </c>
+      <c r="F4" s="15">
         <v>-342.81810000000002</v>
       </c>
     </row>
@@ -1313,13 +1312,13 @@
       <c r="C5" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D5" s="16">
+      <c r="D5" s="15">
         <v>342.81800000000004</v>
       </c>
-      <c r="E5" s="16">
-        <v>0</v>
-      </c>
-      <c r="F5" s="16">
+      <c r="E5" s="15">
+        <v>0</v>
+      </c>
+      <c r="F5" s="15">
         <v>342.81800000000004</v>
       </c>
     </row>
@@ -1333,13 +1332,13 @@
       <c r="C6" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D6" s="16">
+      <c r="D6" s="15">
         <v>1900</v>
       </c>
-      <c r="E6" s="16">
-        <v>0</v>
-      </c>
-      <c r="F6" s="16">
+      <c r="E6" s="15">
+        <v>0</v>
+      </c>
+      <c r="F6" s="15">
         <v>1900</v>
       </c>
     </row>
@@ -1353,13 +1352,13 @@
       <c r="C7" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D7" s="16">
+      <c r="D7" s="15">
         <v>1432.2506000000001</v>
       </c>
-      <c r="E7" s="16">
+      <c r="E7" s="15">
         <v>-0.00010000000005305765</v>
       </c>
-      <c r="F7" s="16">
+      <c r="F7" s="15">
         <v>1432.2505000000001</v>
       </c>
     </row>
@@ -1373,13 +1372,13 @@
       <c r="C8" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D8" s="16">
+      <c r="D8" s="15">
         <v>-124.9314</v>
       </c>
-      <c r="E8" s="16">
+      <c r="E8" s="15">
         <v>-342.81810000000002</v>
       </c>
-      <c r="F8" s="16">
+      <c r="F8" s="15">
         <v>-467.74950000000001</v>
       </c>
     </row>
@@ -1393,13 +1392,13 @@
       <c r="C9" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="16">
+      <c r="D9" s="15">
         <v>-342.81799999999998</v>
       </c>
-      <c r="E9" s="16">
+      <c r="E9" s="15">
         <v>342.81799999999998</v>
       </c>
-      <c r="F9" s="16">
+      <c r="F9" s="15">
         <v>0</v>
       </c>
     </row>
@@ -1413,13 +1412,13 @@
       <c r="C10" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="16">
-        <v>0</v>
-      </c>
-      <c r="E10" s="16">
+      <c r="D10" s="15">
+        <v>0</v>
+      </c>
+      <c r="E10" s="15">
         <v>1900</v>
       </c>
-      <c r="F10" s="16">
+      <c r="F10" s="15">
         <v>1900</v>
       </c>
     </row>
@@ -1433,13 +1432,13 @@
       <c r="C11" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D11" s="16">
+      <c r="D11" s="15">
         <v>-138.31709999999998</v>
       </c>
-      <c r="E11" s="16">
+      <c r="E11" s="15">
         <v>1432.2505000000001</v>
       </c>
-      <c r="F11" s="16">
+      <c r="F11" s="15">
         <v>1293.9333999999999</v>
       </c>
     </row>
@@ -1453,13 +1452,13 @@
       <c r="C12" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D12" s="16">
+      <c r="D12" s="15">
         <v>-138.31709999999998</v>
       </c>
-      <c r="E12" s="16">
+      <c r="E12" s="15">
         <v>-467.74950000000001</v>
       </c>
-      <c r="F12" s="16">
+      <c r="F12" s="15">
         <v>-606.06659999999999</v>
       </c>
     </row>
@@ -1473,13 +1472,13 @@
       <c r="C13" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D13" s="16">
-        <v>0</v>
-      </c>
-      <c r="E13" s="16">
-        <v>0</v>
-      </c>
-      <c r="F13" s="16">
+      <c r="D13" s="15">
+        <v>0</v>
+      </c>
+      <c r="E13" s="15">
+        <v>0</v>
+      </c>
+      <c r="F13" s="15">
         <v>0</v>
       </c>
     </row>
@@ -1493,13 +1492,13 @@
       <c r="C14" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D14" s="16">
-        <v>0</v>
-      </c>
-      <c r="E14" s="16">
+      <c r="D14" s="15">
+        <v>0</v>
+      </c>
+      <c r="E14" s="15">
         <v>1900</v>
       </c>
-      <c r="F14" s="16">
+      <c r="F14" s="15">
         <v>1900</v>
       </c>
     </row>
@@ -1513,13 +1512,13 @@
       <c r="C15" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D15" s="16">
+      <c r="D15" s="15">
         <v>-310.98059999999998</v>
       </c>
-      <c r="E15" s="16">
+      <c r="E15" s="15">
         <v>1293.9333999999999</v>
       </c>
-      <c r="F15" s="16">
+      <c r="F15" s="15">
         <v>982.9527999999998</v>
       </c>
     </row>
@@ -1533,13 +1532,13 @@
       <c r="C16" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D16" s="16">
+      <c r="D16" s="15">
         <v>-310.98059999999998</v>
       </c>
-      <c r="E16" s="16">
+      <c r="E16" s="15">
         <v>-606.06660000000011</v>
       </c>
-      <c r="F16" s="16">
+      <c r="F16" s="15">
         <v>-917.04719999999998</v>
       </c>
     </row>
@@ -1553,13 +1552,13 @@
       <c r="C17" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D17" s="16">
-        <v>0</v>
-      </c>
-      <c r="E17" s="16">
-        <v>0</v>
-      </c>
-      <c r="F17" s="16">
+      <c r="D17" s="15">
+        <v>0</v>
+      </c>
+      <c r="E17" s="15">
+        <v>0</v>
+      </c>
+      <c r="F17" s="15">
         <v>0</v>
       </c>
     </row>
@@ -1573,13 +1572,13 @@
       <c r="C18" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D18" s="16">
+      <c r="D18" s="15">
         <v>600</v>
       </c>
-      <c r="E18" s="16">
+      <c r="E18" s="15">
         <v>1900</v>
       </c>
-      <c r="F18" s="16">
+      <c r="F18" s="15">
         <v>2500</v>
       </c>
     </row>
@@ -1593,13 +1592,13 @@
       <c r="C19" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D19" s="16">
+      <c r="D19" s="15">
         <v>411.26340000000005</v>
       </c>
-      <c r="E19" s="16">
+      <c r="E19" s="15">
         <v>982.9527999999998</v>
       </c>
-      <c r="F19" s="16">
+      <c r="F19" s="15">
         <v>1394.2161999999998</v>
       </c>
     </row>
@@ -1613,13 +1612,13 @@
       <c r="C20" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D20" s="16">
+      <c r="D20" s="15">
         <v>-188.73660000000001</v>
       </c>
-      <c r="E20" s="16">
+      <c r="E20" s="15">
         <v>-917.04719999999998</v>
       </c>
-      <c r="F20" s="16">
+      <c r="F20" s="15">
         <v>-1105.7838000000002</v>
       </c>
     </row>
@@ -1633,13 +1632,13 @@
       <c r="C21" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D21" s="16">
-        <v>0</v>
-      </c>
-      <c r="E21" s="16">
-        <v>0</v>
-      </c>
-      <c r="F21" s="16">
+      <c r="D21" s="15">
+        <v>0</v>
+      </c>
+      <c r="E21" s="15">
+        <v>0</v>
+      </c>
+      <c r="F21" s="15">
         <v>0</v>
       </c>
     </row>
@@ -1671,10 +1670,10 @@
   </cols>
   <sheetData>
     <row r="1" ht="15">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>42</v>
       </c>
     </row>
@@ -1708,13 +1707,13 @@
       <c r="C3" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D3" s="16">
-        <v>0</v>
-      </c>
-      <c r="E3" s="16">
-        <v>0</v>
-      </c>
-      <c r="F3" s="16">
+      <c r="D3" s="15">
+        <v>0</v>
+      </c>
+      <c r="E3" s="15">
+        <v>0</v>
+      </c>
+      <c r="F3" s="15">
         <v>0</v>
       </c>
     </row>
@@ -1728,13 +1727,13 @@
       <c r="C4" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D4" s="16">
+      <c r="D4" s="15">
         <v>-685.63599999999997</v>
       </c>
-      <c r="E4" s="16">
-        <v>0</v>
-      </c>
-      <c r="F4" s="16">
+      <c r="E4" s="15">
+        <v>0</v>
+      </c>
+      <c r="F4" s="15">
         <v>-685.63599999999997</v>
       </c>
     </row>
@@ -1748,13 +1747,13 @@
       <c r="C5" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D5" s="16">
+      <c r="D5" s="15">
         <v>685.63599999999997</v>
       </c>
-      <c r="E5" s="16">
-        <v>0</v>
-      </c>
-      <c r="F5" s="16">
+      <c r="E5" s="15">
+        <v>0</v>
+      </c>
+      <c r="F5" s="15">
         <v>685.63599999999997</v>
       </c>
     </row>
@@ -1768,13 +1767,13 @@
       <c r="C6" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D6" s="16">
+      <c r="D6" s="15">
         <v>3800</v>
       </c>
-      <c r="E6" s="16">
-        <v>0</v>
-      </c>
-      <c r="F6" s="16">
+      <c r="E6" s="15">
+        <v>0</v>
+      </c>
+      <c r="F6" s="15">
         <v>3800</v>
       </c>
     </row>
@@ -1788,13 +1787,13 @@
       <c r="C7" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D7" s="16">
+      <c r="D7" s="15">
         <v>2864.5010000000002</v>
       </c>
-      <c r="E7" s="16">
-        <v>0</v>
-      </c>
-      <c r="F7" s="16">
+      <c r="E7" s="15">
+        <v>0</v>
+      </c>
+      <c r="F7" s="15">
         <v>2864.5010000000002</v>
       </c>
     </row>
@@ -1808,13 +1807,13 @@
       <c r="C8" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D8" s="16">
+      <c r="D8" s="15">
         <v>-249.863</v>
       </c>
-      <c r="E8" s="16">
+      <c r="E8" s="15">
         <v>-685.63599999999997</v>
       </c>
-      <c r="F8" s="16">
+      <c r="F8" s="15">
         <v>-935.49900000000002</v>
       </c>
     </row>
@@ -1828,13 +1827,13 @@
       <c r="C9" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D9" s="16">
+      <c r="D9" s="15">
         <v>-685.63599999999997</v>
       </c>
-      <c r="E9" s="16">
+      <c r="E9" s="15">
         <v>685.63599999999997</v>
       </c>
-      <c r="F9" s="16">
+      <c r="F9" s="15">
         <v>0</v>
       </c>
     </row>
@@ -1848,13 +1847,13 @@
       <c r="C10" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D10" s="16">
-        <v>0</v>
-      </c>
-      <c r="E10" s="16">
+      <c r="D10" s="15">
+        <v>0</v>
+      </c>
+      <c r="E10" s="15">
         <v>3800</v>
       </c>
-      <c r="F10" s="16">
+      <c r="F10" s="15">
         <v>3800</v>
       </c>
     </row>
@@ -1868,13 +1867,13 @@
       <c r="C11" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D11" s="16">
+      <c r="D11" s="15">
         <v>-276.63409999999999</v>
       </c>
-      <c r="E11" s="16">
+      <c r="E11" s="15">
         <v>2864.5010000000002</v>
       </c>
-      <c r="F11" s="16">
+      <c r="F11" s="15">
         <v>2587.8669</v>
       </c>
     </row>
@@ -1888,13 +1887,13 @@
       <c r="C12" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D12" s="16">
+      <c r="D12" s="15">
         <v>-276.63409999999999</v>
       </c>
-      <c r="E12" s="16">
+      <c r="E12" s="15">
         <v>-935.49900000000002</v>
       </c>
-      <c r="F12" s="16">
+      <c r="F12" s="15">
         <v>-1212.1331</v>
       </c>
     </row>
@@ -1908,13 +1907,13 @@
       <c r="C13" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D13" s="16">
-        <v>0</v>
-      </c>
-      <c r="E13" s="16">
-        <v>0</v>
-      </c>
-      <c r="F13" s="16">
+      <c r="D13" s="15">
+        <v>0</v>
+      </c>
+      <c r="E13" s="15">
+        <v>0</v>
+      </c>
+      <c r="F13" s="15">
         <v>0</v>
       </c>
     </row>
@@ -1928,13 +1927,13 @@
       <c r="C14" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D14" s="16">
-        <v>0</v>
-      </c>
-      <c r="E14" s="16">
+      <c r="D14" s="15">
+        <v>0</v>
+      </c>
+      <c r="E14" s="15">
         <v>3800</v>
       </c>
-      <c r="F14" s="16">
+      <c r="F14" s="15">
         <v>3800</v>
       </c>
     </row>
@@ -1948,13 +1947,13 @@
       <c r="C15" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D15" s="16">
+      <c r="D15" s="15">
         <v>-621.96130000000005</v>
       </c>
-      <c r="E15" s="16">
+      <c r="E15" s="15">
         <v>2587.8669</v>
       </c>
-      <c r="F15" s="16">
+      <c r="F15" s="15">
         <v>1965.9056</v>
       </c>
     </row>
@@ -1968,13 +1967,13 @@
       <c r="C16" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D16" s="16">
+      <c r="D16" s="15">
         <v>-621.96130000000005</v>
       </c>
-      <c r="E16" s="16">
+      <c r="E16" s="15">
         <v>-1212.1331</v>
       </c>
-      <c r="F16" s="16">
+      <c r="F16" s="15">
         <v>-1834.0944</v>
       </c>
     </row>
@@ -1988,13 +1987,13 @@
       <c r="C17" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D17" s="16">
-        <v>0</v>
-      </c>
-      <c r="E17" s="16">
-        <v>0</v>
-      </c>
-      <c r="F17" s="16">
+      <c r="D17" s="15">
+        <v>0</v>
+      </c>
+      <c r="E17" s="15">
+        <v>0</v>
+      </c>
+      <c r="F17" s="15">
         <v>0</v>
       </c>
     </row>
@@ -2008,13 +2007,13 @@
       <c r="C18" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D18" s="16">
+      <c r="D18" s="15">
         <v>1200</v>
       </c>
-      <c r="E18" s="16">
+      <c r="E18" s="15">
         <v>3800</v>
       </c>
-      <c r="F18" s="16">
+      <c r="F18" s="15">
         <v>5000</v>
       </c>
     </row>
@@ -2028,13 +2027,13 @@
       <c r="C19" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D19" s="16">
+      <c r="D19" s="15">
         <v>822.52660000000003</v>
       </c>
-      <c r="E19" s="16">
+      <c r="E19" s="15">
         <v>1965.9056</v>
       </c>
-      <c r="F19" s="16">
+      <c r="F19" s="15">
         <v>2788.4322000000002</v>
       </c>
     </row>
@@ -2048,13 +2047,13 @@
       <c r="C20" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D20" s="16">
+      <c r="D20" s="15">
         <v>-377.47340000000003</v>
       </c>
-      <c r="E20" s="16">
+      <c r="E20" s="15">
         <v>-1834.0944</v>
       </c>
-      <c r="F20" s="16">
+      <c r="F20" s="15">
         <v>-2211.5677999999998</v>
       </c>
     </row>
@@ -2068,13 +2067,13 @@
       <c r="C21" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D21" s="16">
-        <v>0</v>
-      </c>
-      <c r="E21" s="16">
-        <v>0</v>
-      </c>
-      <c r="F21" s="16">
+      <c r="D21" s="15">
+        <v>0</v>
+      </c>
+      <c r="E21" s="15">
+        <v>0</v>
+      </c>
+      <c r="F21" s="15">
         <v>0</v>
       </c>
     </row>
@@ -2101,10 +2100,10 @@
   </cols>
   <sheetData>
     <row r="1" ht="15">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>44</v>
       </c>
     </row>
@@ -2138,13 +2137,13 @@
       <c r="C3" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D3" s="16">
-        <v>0</v>
-      </c>
-      <c r="E3" s="16">
-        <v>0</v>
-      </c>
-      <c r="F3" s="16">
+      <c r="D3" s="15">
+        <v>0</v>
+      </c>
+      <c r="E3" s="15">
+        <v>0</v>
+      </c>
+      <c r="F3" s="15">
         <v>0</v>
       </c>
     </row>
@@ -2158,13 +2157,13 @@
       <c r="C4" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D4" s="16">
+      <c r="D4" s="15">
         <v>-1028.454</v>
       </c>
-      <c r="E4" s="16">
-        <v>0</v>
-      </c>
-      <c r="F4" s="16">
+      <c r="E4" s="15">
+        <v>0</v>
+      </c>
+      <c r="F4" s="15">
         <v>-1028.454</v>
       </c>
     </row>
@@ -2178,13 +2177,13 @@
       <c r="C5" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D5" s="16">
+      <c r="D5" s="15">
         <v>1028.454</v>
       </c>
-      <c r="E5" s="16">
-        <v>0</v>
-      </c>
-      <c r="F5" s="16">
+      <c r="E5" s="15">
+        <v>0</v>
+      </c>
+      <c r="F5" s="15">
         <v>1028.454</v>
       </c>
     </row>
@@ -2198,13 +2197,13 @@
       <c r="C6" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D6" s="16">
+      <c r="D6" s="15">
         <v>5700</v>
       </c>
-      <c r="E6" s="16">
-        <v>0</v>
-      </c>
-      <c r="F6" s="16">
+      <c r="E6" s="15">
+        <v>0</v>
+      </c>
+      <c r="F6" s="15">
         <v>5700</v>
       </c>
     </row>
@@ -2218,13 +2217,13 @@
       <c r="C7" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D7" s="16">
+      <c r="D7" s="15">
         <v>4296.7515000000003</v>
       </c>
-      <c r="E7" s="16">
-        <v>0</v>
-      </c>
-      <c r="F7" s="16">
+      <c r="E7" s="15">
+        <v>0</v>
+      </c>
+      <c r="F7" s="15">
         <v>4296.7515000000003</v>
       </c>
     </row>
@@ -2238,13 +2237,13 @@
       <c r="C8" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D8" s="16">
+      <c r="D8" s="15">
         <v>-374.79450000000003</v>
       </c>
-      <c r="E8" s="16">
+      <c r="E8" s="15">
         <v>-1028.454</v>
       </c>
-      <c r="F8" s="16">
+      <c r="F8" s="15">
         <v>-1403.2484999999999</v>
       </c>
     </row>
@@ -2258,13 +2257,13 @@
       <c r="C9" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D9" s="16">
+      <c r="D9" s="15">
         <v>-1028.454</v>
       </c>
-      <c r="E9" s="16">
+      <c r="E9" s="15">
         <v>1028.454</v>
       </c>
-      <c r="F9" s="16">
+      <c r="F9" s="15">
         <v>0</v>
       </c>
     </row>
@@ -2278,13 +2277,13 @@
       <c r="C10" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D10" s="16">
-        <v>0</v>
-      </c>
-      <c r="E10" s="16">
+      <c r="D10" s="15">
+        <v>0</v>
+      </c>
+      <c r="E10" s="15">
         <v>5700</v>
       </c>
-      <c r="F10" s="16">
+      <c r="F10" s="15">
         <v>5700</v>
       </c>
     </row>
@@ -2298,13 +2297,13 @@
       <c r="C11" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D11" s="16">
+      <c r="D11" s="15">
         <v>-414.9511</v>
       </c>
-      <c r="E11" s="16">
+      <c r="E11" s="15">
         <v>4296.7515000000003</v>
       </c>
-      <c r="F11" s="16">
+      <c r="F11" s="15">
         <v>3881.8004000000001</v>
       </c>
     </row>
@@ -2318,13 +2317,13 @@
       <c r="C12" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D12" s="16">
+      <c r="D12" s="15">
         <v>-414.9511</v>
       </c>
-      <c r="E12" s="16">
+      <c r="E12" s="15">
         <v>-1403.2484999999999</v>
       </c>
-      <c r="F12" s="16">
+      <c r="F12" s="15">
         <v>-1818.1995999999999</v>
       </c>
     </row>
@@ -2338,13 +2337,13 @@
       <c r="C13" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D13" s="16">
-        <v>0</v>
-      </c>
-      <c r="E13" s="16">
-        <v>0</v>
-      </c>
-      <c r="F13" s="16">
+      <c r="D13" s="15">
+        <v>0</v>
+      </c>
+      <c r="E13" s="15">
+        <v>0</v>
+      </c>
+      <c r="F13" s="15">
         <v>0</v>
       </c>
     </row>
@@ -2358,13 +2357,13 @@
       <c r="C14" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D14" s="16">
-        <v>0</v>
-      </c>
-      <c r="E14" s="16">
+      <c r="D14" s="15">
+        <v>0</v>
+      </c>
+      <c r="E14" s="15">
         <v>5700</v>
       </c>
-      <c r="F14" s="16">
+      <c r="F14" s="15">
         <v>5700</v>
       </c>
     </row>
@@ -2378,13 +2377,13 @@
       <c r="C15" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D15" s="16">
+      <c r="D15" s="15">
         <v>-932.94190000000003</v>
       </c>
-      <c r="E15" s="16">
+      <c r="E15" s="15">
         <v>3881.8004000000001</v>
       </c>
-      <c r="F15" s="16">
+      <c r="F15" s="15">
         <v>2948.8584999999998</v>
       </c>
     </row>
@@ -2398,13 +2397,13 @@
       <c r="C16" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D16" s="16">
+      <c r="D16" s="15">
         <v>-932.94190000000003</v>
       </c>
-      <c r="E16" s="16">
+      <c r="E16" s="15">
         <v>-1818.1995999999999</v>
       </c>
-      <c r="F16" s="16">
+      <c r="F16" s="15">
         <v>-2751.1415000000002</v>
       </c>
     </row>
@@ -2418,13 +2417,13 @@
       <c r="C17" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D17" s="16">
-        <v>0</v>
-      </c>
-      <c r="E17" s="16">
-        <v>0</v>
-      </c>
-      <c r="F17" s="16">
+      <c r="D17" s="15">
+        <v>0</v>
+      </c>
+      <c r="E17" s="15">
+        <v>0</v>
+      </c>
+      <c r="F17" s="15">
         <v>0</v>
       </c>
     </row>
@@ -2438,13 +2437,13 @@
       <c r="C18" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D18" s="16">
+      <c r="D18" s="15">
         <v>1800</v>
       </c>
-      <c r="E18" s="16">
+      <c r="E18" s="15">
         <v>5700</v>
       </c>
-      <c r="F18" s="16">
+      <c r="F18" s="15">
         <v>7500</v>
       </c>
     </row>
@@ -2458,13 +2457,13 @@
       <c r="C19" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D19" s="16">
+      <c r="D19" s="15">
         <v>1233.79</v>
       </c>
-      <c r="E19" s="16">
+      <c r="E19" s="15">
         <v>2948.8584999999998</v>
       </c>
-      <c r="F19" s="16">
+      <c r="F19" s="15">
         <v>4182.6485000000002</v>
       </c>
     </row>
@@ -2478,13 +2477,13 @@
       <c r="C20" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D20" s="16">
+      <c r="D20" s="15">
         <v>-566.21000000000004</v>
       </c>
-      <c r="E20" s="16">
+      <c r="E20" s="15">
         <v>-2751.1415000000002</v>
       </c>
-      <c r="F20" s="16">
+      <c r="F20" s="15">
         <v>-3317.3515000000002</v>
       </c>
     </row>
@@ -2498,13 +2497,13 @@
       <c r="C21" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D21" s="16">
-        <v>0</v>
-      </c>
-      <c r="E21" s="16">
-        <v>0</v>
-      </c>
-      <c r="F21" s="16">
+      <c r="D21" s="15">
+        <v>0</v>
+      </c>
+      <c r="E21" s="15">
+        <v>0</v>
+      </c>
+      <c r="F21" s="15">
         <v>0</v>
       </c>
     </row>
@@ -2531,10 +2530,10 @@
   </cols>
   <sheetData>
     <row r="1" ht="15">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>46</v>
       </c>
     </row>
@@ -2568,13 +2567,13 @@
       <c r="C3" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D3" s="16">
-        <v>0</v>
-      </c>
-      <c r="E3" s="16">
-        <v>0</v>
-      </c>
-      <c r="F3" s="16">
+      <c r="D3" s="15">
+        <v>0</v>
+      </c>
+      <c r="E3" s="15">
+        <v>0</v>
+      </c>
+      <c r="F3" s="15">
         <v>0</v>
       </c>
     </row>
@@ -2588,13 +2587,13 @@
       <c r="C4" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D4" s="16">
+      <c r="D4" s="15">
         <v>-1371.2719999999999</v>
       </c>
-      <c r="E4" s="16">
-        <v>0</v>
-      </c>
-      <c r="F4" s="16">
+      <c r="E4" s="15">
+        <v>0</v>
+      </c>
+      <c r="F4" s="15">
         <v>-1371.2719999999999</v>
       </c>
     </row>
@@ -2608,13 +2607,13 @@
       <c r="C5" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D5" s="16">
+      <c r="D5" s="15">
         <v>1371.2719999999999</v>
       </c>
-      <c r="E5" s="16">
-        <v>0</v>
-      </c>
-      <c r="F5" s="16">
+      <c r="E5" s="15">
+        <v>0</v>
+      </c>
+      <c r="F5" s="15">
         <v>1371.2719999999999</v>
       </c>
     </row>
@@ -2628,13 +2627,13 @@
       <c r="C6" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D6" s="16">
+      <c r="D6" s="15">
         <v>7600</v>
       </c>
-      <c r="E6" s="16">
-        <v>0</v>
-      </c>
-      <c r="F6" s="16">
+      <c r="E6" s="15">
+        <v>0</v>
+      </c>
+      <c r="F6" s="15">
         <v>7600</v>
       </c>
     </row>
@@ -2648,13 +2647,13 @@
       <c r="C7" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D7" s="16">
+      <c r="D7" s="15">
         <v>5729.0019000000002</v>
       </c>
-      <c r="E7" s="16">
-        <v>0</v>
-      </c>
-      <c r="F7" s="16">
+      <c r="E7" s="15">
+        <v>0</v>
+      </c>
+      <c r="F7" s="15">
         <v>5729.0019000000002</v>
       </c>
     </row>
@@ -2668,13 +2667,13 @@
       <c r="C8" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D8" s="16">
+      <c r="D8" s="15">
         <v>-499.72609999999997</v>
       </c>
-      <c r="E8" s="16">
+      <c r="E8" s="15">
         <v>-1371.2719999999999</v>
       </c>
-      <c r="F8" s="16">
+      <c r="F8" s="15">
         <v>-1870.9981</v>
       </c>
     </row>
@@ -2688,13 +2687,13 @@
       <c r="C9" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D9" s="16">
+      <c r="D9" s="15">
         <v>-1371.2719999999999</v>
       </c>
-      <c r="E9" s="16">
+      <c r="E9" s="15">
         <v>1371.2719999999999</v>
       </c>
-      <c r="F9" s="16">
+      <c r="F9" s="15">
         <v>0</v>
       </c>
     </row>
@@ -2708,13 +2707,13 @@
       <c r="C10" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D10" s="16">
-        <v>0</v>
-      </c>
-      <c r="E10" s="16">
+      <c r="D10" s="15">
+        <v>0</v>
+      </c>
+      <c r="E10" s="15">
         <v>7600</v>
       </c>
-      <c r="F10" s="16">
+      <c r="F10" s="15">
         <v>7600</v>
       </c>
     </row>
@@ -2728,13 +2727,13 @@
       <c r="C11" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D11" s="16">
+      <c r="D11" s="15">
         <v>-553.2681</v>
       </c>
-      <c r="E11" s="16">
+      <c r="E11" s="15">
         <v>5729.0019000000002</v>
       </c>
-      <c r="F11" s="16">
+      <c r="F11" s="15">
         <v>5175.7338</v>
       </c>
     </row>
@@ -2748,13 +2747,13 @@
       <c r="C12" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D12" s="16">
+      <c r="D12" s="15">
         <v>-553.2681</v>
       </c>
-      <c r="E12" s="16">
+      <c r="E12" s="15">
         <v>-1870.9981</v>
       </c>
-      <c r="F12" s="16">
+      <c r="F12" s="15">
         <v>-2424.2662</v>
       </c>
     </row>
@@ -2768,13 +2767,13 @@
       <c r="C13" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D13" s="16">
-        <v>0</v>
-      </c>
-      <c r="E13" s="16">
-        <v>0</v>
-      </c>
-      <c r="F13" s="16">
+      <c r="D13" s="15">
+        <v>0</v>
+      </c>
+      <c r="E13" s="15">
+        <v>0</v>
+      </c>
+      <c r="F13" s="15">
         <v>0</v>
       </c>
     </row>
@@ -2788,13 +2787,13 @@
       <c r="C14" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D14" s="16">
-        <v>0</v>
-      </c>
-      <c r="E14" s="16">
+      <c r="D14" s="15">
+        <v>0</v>
+      </c>
+      <c r="E14" s="15">
         <v>7600</v>
       </c>
-      <c r="F14" s="16">
+      <c r="F14" s="15">
         <v>7600</v>
       </c>
     </row>
@@ -2808,13 +2807,13 @@
       <c r="C15" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D15" s="16">
+      <c r="D15" s="15">
         <v>-1243.9224999999999</v>
       </c>
-      <c r="E15" s="16">
+      <c r="E15" s="15">
         <v>5175.7338</v>
       </c>
-      <c r="F15" s="16">
+      <c r="F15" s="15">
         <v>3931.8112999999998</v>
       </c>
     </row>
@@ -2828,13 +2827,13 @@
       <c r="C16" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D16" s="16">
+      <c r="D16" s="15">
         <v>-1243.9224999999999</v>
       </c>
-      <c r="E16" s="16">
+      <c r="E16" s="15">
         <v>-2424.2662</v>
       </c>
-      <c r="F16" s="16">
+      <c r="F16" s="15">
         <v>-3668.1887000000002</v>
       </c>
     </row>
@@ -2848,13 +2847,13 @@
       <c r="C17" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D17" s="16">
-        <v>0</v>
-      </c>
-      <c r="E17" s="16">
-        <v>0</v>
-      </c>
-      <c r="F17" s="16">
+      <c r="D17" s="15">
+        <v>0</v>
+      </c>
+      <c r="E17" s="15">
+        <v>0</v>
+      </c>
+      <c r="F17" s="15">
         <v>0</v>
       </c>
     </row>
@@ -2868,13 +2867,13 @@
       <c r="C18" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D18" s="16">
+      <c r="D18" s="15">
         <v>2400</v>
       </c>
-      <c r="E18" s="16">
+      <c r="E18" s="15">
         <v>7600</v>
       </c>
-      <c r="F18" s="16">
+      <c r="F18" s="15">
         <v>10000</v>
       </c>
     </row>
@@ -2888,13 +2887,13 @@
       <c r="C19" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D19" s="16">
+      <c r="D19" s="15">
         <v>1645.0532000000001</v>
       </c>
-      <c r="E19" s="16">
+      <c r="E19" s="15">
         <v>3931.8112999999998</v>
       </c>
-      <c r="F19" s="16">
+      <c r="F19" s="15">
         <v>5576.8644999999997</v>
       </c>
     </row>
@@ -2908,13 +2907,13 @@
       <c r="C20" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D20" s="16">
+      <c r="D20" s="15">
         <v>-754.94680000000005</v>
       </c>
-      <c r="E20" s="16">
+      <c r="E20" s="15">
         <v>-3668.1887000000002</v>
       </c>
-      <c r="F20" s="16">
+      <c r="F20" s="15">
         <v>-4423.1355000000003</v>
       </c>
     </row>
@@ -2928,13 +2927,13 @@
       <c r="C21" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D21" s="16">
-        <v>0</v>
-      </c>
-      <c r="E21" s="16">
-        <v>0</v>
-      </c>
-      <c r="F21" s="16">
+      <c r="D21" s="15">
+        <v>0</v>
+      </c>
+      <c r="E21" s="15">
+        <v>0</v>
+      </c>
+      <c r="F21" s="15">
         <v>0</v>
       </c>
     </row>
@@ -2958,555 +2957,555 @@
   </cols>
   <sheetData>
     <row r="1" ht="15">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="G1" s="7"/>
+      <c r="G1" s="6"/>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="G2" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="I2" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="J2" s="8" t="s">
+      <c r="J2" s="7" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12">
+      <c r="A3" s="11">
         <v>20220131</v>
       </c>
-      <c r="B3" s="12">
-        <v>0</v>
-      </c>
-      <c r="C3" s="12" t="s">
+      <c r="B3" s="11">
+        <v>0</v>
+      </c>
+      <c r="C3" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="E3" s="12">
+      <c r="E3" s="11">
         <v>20220131</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="F3" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="G3" s="13">
+      <c r="G3" s="12">
         <v>1714.0899999999999</v>
       </c>
-      <c r="H3" s="12">
+      <c r="H3" s="11">
         <v>202201</v>
       </c>
-      <c r="I3" s="12">
+      <c r="I3" s="11">
         <v>202201</v>
       </c>
-      <c r="J3" s="12">
+      <c r="J3" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12">
+      <c r="A4" s="11">
         <v>20220131</v>
       </c>
-      <c r="B4" s="12">
+      <c r="B4" s="11">
         <v>2</v>
       </c>
-      <c r="C4" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="D4" s="12" t="s">
+      <c r="C4" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="D4" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="E4" s="12">
+      <c r="E4" s="11">
         <v>20220131</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="F4" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="G4" s="13">
+      <c r="G4" s="12">
         <v>-237.9648</v>
       </c>
-      <c r="H4" s="12">
+      <c r="H4" s="11">
         <v>202201</v>
       </c>
-      <c r="I4" s="12">
+      <c r="I4" s="11">
         <v>202201</v>
       </c>
-      <c r="J4" s="12">
+      <c r="J4" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="12">
+      <c r="A5" s="11">
         <v>20220131</v>
       </c>
-      <c r="B5" s="12">
+      <c r="B5" s="11">
         <v>3</v>
       </c>
-      <c r="C5" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="D5" s="12" t="s">
+      <c r="C5" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="11">
         <v>20220131</v>
       </c>
-      <c r="F5" s="12" t="s">
+      <c r="F5" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="G5" s="13">
+      <c r="G5" s="12">
         <v>-1357.1429000000001</v>
       </c>
-      <c r="H5" s="12">
+      <c r="H5" s="11">
         <v>202201</v>
       </c>
-      <c r="I5" s="12">
+      <c r="I5" s="11">
         <v>202201</v>
       </c>
-      <c r="J5" s="12">
+      <c r="J5" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="6" ht="12.75" customHeight="1">
-      <c r="A6" s="12">
+      <c r="A6" s="11">
         <v>20220131</v>
       </c>
-      <c r="B6" s="12">
+      <c r="B6" s="11">
         <v>4</v>
       </c>
-      <c r="C6" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="D6" s="12" t="s">
+      <c r="C6" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="E6" s="12">
+      <c r="E6" s="11">
         <v>20220131</v>
       </c>
-      <c r="F6" s="12" t="s">
+      <c r="F6" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="G6" s="13">
+      <c r="G6" s="12">
         <v>-118.9824</v>
       </c>
-      <c r="H6" s="12">
+      <c r="H6" s="11">
         <v>202201</v>
       </c>
-      <c r="I6" s="12">
+      <c r="I6" s="11">
         <v>202201</v>
       </c>
-      <c r="J6" s="12">
+      <c r="J6" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="7" ht="12.75" customHeight="1">
-      <c r="A7" s="12">
+      <c r="A7" s="11">
         <v>20220228</v>
       </c>
-      <c r="B7" s="12">
-        <v>0</v>
-      </c>
-      <c r="C7" s="12" t="s">
+      <c r="B7" s="11">
+        <v>0</v>
+      </c>
+      <c r="C7" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="E7" s="12">
+      <c r="E7" s="11">
         <v>20220228</v>
       </c>
-      <c r="F7" s="12" t="s">
+      <c r="F7" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="G7" s="13">
+      <c r="G7" s="12">
         <v>9500</v>
       </c>
-      <c r="H7" s="12">
+      <c r="H7" s="11">
         <v>202202</v>
       </c>
-      <c r="I7" s="12">
+      <c r="I7" s="11">
         <v>202202</v>
       </c>
-      <c r="J7" s="12">
+      <c r="J7" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="8" ht="12.75" customHeight="1">
-      <c r="A8" s="12">
+      <c r="A8" s="11">
         <v>20220228</v>
       </c>
-      <c r="B8" s="12">
-        <v>0</v>
-      </c>
-      <c r="C8" s="12" t="s">
+      <c r="B8" s="11">
+        <v>0</v>
+      </c>
+      <c r="C8" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="11">
         <v>20220228</v>
       </c>
-      <c r="F8" s="12" t="s">
+      <c r="F8" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="G8" s="13">
+      <c r="G8" s="12">
         <v>-1714.0899999999999</v>
       </c>
-      <c r="H8" s="12">
+      <c r="H8" s="11">
         <v>202202</v>
       </c>
-      <c r="I8" s="12">
+      <c r="I8" s="11">
         <v>202202</v>
       </c>
-      <c r="J8" s="12">
+      <c r="J8" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="9" ht="12.75" customHeight="1">
-      <c r="A9" s="12">
+      <c r="A9" s="11">
         <v>20220228</v>
       </c>
-      <c r="B9" s="12">
+      <c r="B9" s="11">
         <v>2</v>
       </c>
-      <c r="C9" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="D9" s="12" t="s">
+      <c r="C9" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="E9" s="12">
+      <c r="E9" s="11">
         <v>20220228</v>
       </c>
-      <c r="F9" s="12" t="s">
+      <c r="F9" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="G9" s="13">
+      <c r="G9" s="12">
         <v>-416.43830000000003</v>
       </c>
-      <c r="H9" s="12">
+      <c r="H9" s="11">
         <v>202202</v>
       </c>
-      <c r="I9" s="12">
+      <c r="I9" s="11">
         <v>202202</v>
       </c>
-      <c r="J9" s="12">
+      <c r="J9" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="10" ht="12.75" customHeight="1">
-      <c r="A10" s="12">
+      <c r="A10" s="11">
         <v>20220228</v>
       </c>
-      <c r="B10" s="12">
+      <c r="B10" s="11">
         <v>4</v>
       </c>
-      <c r="C10" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="D10" s="12" t="s">
+      <c r="C10" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="E10" s="12">
+      <c r="E10" s="11">
         <v>20220228</v>
       </c>
-      <c r="F10" s="12" t="s">
+      <c r="F10" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="G10" s="13">
+      <c r="G10" s="12">
         <v>-208.2192</v>
       </c>
-      <c r="H10" s="12">
+      <c r="H10" s="11">
         <v>202202</v>
       </c>
-      <c r="I10" s="12">
+      <c r="I10" s="11">
         <v>202202</v>
       </c>
-      <c r="J10" s="12">
+      <c r="J10" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="11" ht="12.75" customHeight="1">
-      <c r="A11" s="12">
+      <c r="A11" s="11">
         <v>20220331</v>
       </c>
-      <c r="B11" s="12">
+      <c r="B11" s="11">
         <v>2</v>
       </c>
-      <c r="C11" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="D11" s="12" t="s">
+      <c r="C11" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="E11" s="12">
+      <c r="E11" s="11">
         <v>20220331</v>
       </c>
-      <c r="F11" s="12" t="s">
+      <c r="F11" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="G11" s="13">
+      <c r="G11" s="12">
         <v>-461.05680000000001</v>
       </c>
-      <c r="H11" s="12">
+      <c r="H11" s="11">
         <v>202203</v>
       </c>
-      <c r="I11" s="12">
+      <c r="I11" s="11">
         <v>202203</v>
       </c>
-      <c r="J11" s="12">
+      <c r="J11" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="12" ht="12.75" customHeight="1">
-      <c r="A12" s="12">
+      <c r="A12" s="11">
         <v>20220331</v>
       </c>
-      <c r="B12" s="12">
+      <c r="B12" s="11">
         <v>4</v>
       </c>
-      <c r="C12" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="D12" s="12" t="s">
+      <c r="C12" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="E12" s="12">
+      <c r="E12" s="11">
         <v>20220331</v>
       </c>
-      <c r="F12" s="12" t="s">
+      <c r="F12" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="G12" s="13">
+      <c r="G12" s="12">
         <v>-230.5283</v>
       </c>
-      <c r="H12" s="12">
+      <c r="H12" s="11">
         <v>202203</v>
       </c>
-      <c r="I12" s="12">
+      <c r="I12" s="11">
         <v>202203</v>
       </c>
-      <c r="J12" s="12">
+      <c r="J12" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="13" ht="12.75" customHeight="1">
-      <c r="A13" s="12">
+      <c r="A13" s="11">
         <v>20220430</v>
       </c>
-      <c r="B13" s="12">
+      <c r="B13" s="11">
         <v>2</v>
       </c>
-      <c r="C13" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="D13" s="12" t="s">
+      <c r="C13" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="D13" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="E13" s="12">
+      <c r="E13" s="11">
         <v>20220430</v>
       </c>
-      <c r="F13" s="12" t="s">
+      <c r="F13" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="G13" s="13">
+      <c r="G13" s="12">
         <v>-482.71359999999999</v>
       </c>
-      <c r="H13" s="12">
+      <c r="H13" s="11">
         <v>202204</v>
       </c>
-      <c r="I13" s="12">
+      <c r="I13" s="11">
         <v>202204</v>
       </c>
-      <c r="J13" s="12">
+      <c r="J13" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="14" ht="12.75" customHeight="1">
-      <c r="A14" s="12">
+      <c r="A14" s="11">
         <v>20220430</v>
       </c>
-      <c r="B14" s="12">
+      <c r="B14" s="11">
         <v>3</v>
       </c>
-      <c r="C14" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="D14" s="12" t="s">
+      <c r="C14" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="D14" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="E14" s="12">
+      <c r="E14" s="11">
         <v>20220430</v>
       </c>
-      <c r="F14" s="12" t="s">
+      <c r="F14" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="G14" s="13">
+      <c r="G14" s="12">
         <v>-31.745999999999999</v>
       </c>
-      <c r="H14" s="12">
+      <c r="H14" s="11">
         <v>202204</v>
       </c>
-      <c r="I14" s="12">
+      <c r="I14" s="11">
         <v>202204</v>
       </c>
-      <c r="J14" s="12">
+      <c r="J14" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="15" ht="12.75" customHeight="1">
-      <c r="A15" s="12">
+      <c r="A15" s="11">
         <v>20220430</v>
       </c>
-      <c r="B15" s="12">
+      <c r="B15" s="11">
         <v>4</v>
       </c>
-      <c r="C15" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="D15" s="12" t="s">
+      <c r="C15" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="E15" s="12">
+      <c r="E15" s="11">
         <v>20220430</v>
       </c>
-      <c r="F15" s="12" t="s">
+      <c r="F15" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="G15" s="13">
+      <c r="G15" s="12">
         <v>-1040.4436000000001</v>
       </c>
-      <c r="H15" s="12">
+      <c r="H15" s="11">
         <v>202204</v>
       </c>
-      <c r="I15" s="12">
+      <c r="I15" s="11">
         <v>202204</v>
       </c>
-      <c r="J15" s="12">
+      <c r="J15" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="16" ht="12.75" customHeight="1">
-      <c r="A16" s="12">
+      <c r="A16" s="11">
         <v>20220531</v>
       </c>
-      <c r="B16" s="12">
-        <v>0</v>
-      </c>
-      <c r="C16" s="12" t="s">
+      <c r="B16" s="11">
+        <v>0</v>
+      </c>
+      <c r="C16" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="D16" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="E16" s="12">
+      <c r="E16" s="11">
         <v>20220531</v>
       </c>
-      <c r="F16" s="12" t="s">
+      <c r="F16" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="G16" s="14">
+      <c r="G16" s="13">
         <v>3000</v>
       </c>
-      <c r="H16" s="12">
+      <c r="H16" s="11">
         <v>202205</v>
       </c>
-      <c r="I16" s="12">
+      <c r="I16" s="11">
         <v>202205</v>
       </c>
-      <c r="J16" s="12">
+      <c r="J16" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="17" ht="12.75" customHeight="1">
-      <c r="A17" s="12">
+      <c r="A17" s="11">
         <v>20220531</v>
       </c>
-      <c r="B17" s="12">
+      <c r="B17" s="11">
         <v>2</v>
       </c>
-      <c r="C17" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="D17" s="12" t="s">
+      <c r="C17" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="D17" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="E17" s="12">
+      <c r="E17" s="11">
         <v>20220531</v>
       </c>
-      <c r="F17" s="12" t="s">
+      <c r="F17" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="G17" s="13">
+      <c r="G17" s="12">
         <v>-471.8417</v>
       </c>
-      <c r="H17" s="12">
+      <c r="H17" s="11">
         <v>202205</v>
       </c>
-      <c r="I17" s="12">
+      <c r="I17" s="11">
         <v>202205</v>
       </c>
-      <c r="J17" s="12">
+      <c r="J17" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="18" ht="12.75" customHeight="1">
-      <c r="A18" s="12">
+      <c r="A18" s="11">
         <v>20220531</v>
       </c>
-      <c r="B18" s="12">
+      <c r="B18" s="11">
         <v>4</v>
       </c>
-      <c r="C18" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="D18" s="12" t="s">
+      <c r="C18" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="D18" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="E18" s="12">
+      <c r="E18" s="11">
         <v>20220531</v>
       </c>
-      <c r="F18" s="12" t="s">
+      <c r="F18" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="G18" s="13">
+      <c r="G18" s="12">
         <v>-471.8417</v>
       </c>
-      <c r="H18" s="12">
+      <c r="H18" s="11">
         <v>202205</v>
       </c>
-      <c r="I18" s="12">
+      <c r="I18" s="11">
         <v>202205</v>
       </c>
-      <c r="J18" s="12">
+      <c r="J18" s="11">
         <v>0</v>
       </c>
     </row>
@@ -3535,10 +3534,10 @@
   </cols>
   <sheetData>
     <row r="1" ht="15">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>58</v>
       </c>
     </row>
@@ -3581,7 +3580,7 @@
       <c r="E3" s="1">
         <v>0</v>
       </c>
-      <c r="F3" s="15">
+      <c r="F3" s="14">
         <v>1714.0899999999999</v>
       </c>
       <c r="G3" s="1">
@@ -3604,7 +3603,7 @@
       <c r="E4" s="1">
         <v>0</v>
       </c>
-      <c r="F4" s="15">
+      <c r="F4" s="14">
         <v>1714.0899999999999</v>
       </c>
       <c r="G4" s="1">
@@ -3627,7 +3626,7 @@
       <c r="E5" s="1">
         <v>0</v>
       </c>
-      <c r="F5" s="15">
+      <c r="F5" s="14">
         <v>-237.9648</v>
       </c>
       <c r="G5" s="1">
@@ -3673,7 +3672,7 @@
       <c r="E7" s="1">
         <v>0</v>
       </c>
-      <c r="F7" s="15">
+      <c r="F7" s="14">
         <v>-1357.1429000000001</v>
       </c>
       <c r="G7" s="1">
@@ -3696,7 +3695,7 @@
       <c r="E8" s="1">
         <v>0</v>
       </c>
-      <c r="F8" s="15">
+      <c r="F8" s="14">
         <v>-1357.1429000000001</v>
       </c>
       <c r="G8" s="1">
@@ -3719,7 +3718,7 @@
       <c r="E9" s="1">
         <v>0</v>
       </c>
-      <c r="F9" s="15">
+      <c r="F9" s="14">
         <v>-118.9824</v>
       </c>
       <c r="G9" s="1">
@@ -3742,7 +3741,7 @@
       <c r="E10" s="1">
         <v>0</v>
       </c>
-      <c r="F10" s="15">
+      <c r="F10" s="14">
         <v>-118.9824</v>
       </c>
       <c r="G10" s="1">
@@ -3765,7 +3764,7 @@
       <c r="E11" s="1">
         <v>0</v>
       </c>
-      <c r="F11" s="15">
+      <c r="F11" s="14">
         <v>9500</v>
       </c>
       <c r="G11" s="1">
@@ -4600,10 +4599,10 @@
   </cols>
   <sheetData>
     <row r="1" ht="15">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>58</v>
       </c>
     </row>
@@ -4637,13 +4636,13 @@
       <c r="C3" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D3" s="16">
+      <c r="D3" s="15">
         <v>-0.0001</v>
       </c>
-      <c r="E3" s="16">
-        <v>0</v>
-      </c>
-      <c r="F3" s="16">
+      <c r="E3" s="15">
+        <v>0</v>
+      </c>
+      <c r="F3" s="15">
         <v>-0.0001</v>
       </c>
     </row>
@@ -4657,13 +4656,13 @@
       <c r="C4" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D4" s="16">
+      <c r="D4" s="15">
         <v>-1714.0900999999999</v>
       </c>
-      <c r="E4" s="16">
-        <v>0</v>
-      </c>
-      <c r="F4" s="16">
+      <c r="E4" s="15">
+        <v>0</v>
+      </c>
+      <c r="F4" s="15">
         <v>-1714.0900999999999</v>
       </c>
     </row>
@@ -4677,13 +4676,13 @@
       <c r="C5" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D5" s="16">
+      <c r="D5" s="15">
         <v>1714.0899999999999</v>
       </c>
-      <c r="E5" s="16">
-        <v>0</v>
-      </c>
-      <c r="F5" s="16">
+      <c r="E5" s="15">
+        <v>0</v>
+      </c>
+      <c r="F5" s="15">
         <v>1714.0899999999999</v>
       </c>
     </row>
@@ -4697,13 +4696,13 @@
       <c r="C6" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D6" s="16">
+      <c r="D6" s="15">
         <v>9500</v>
       </c>
-      <c r="E6" s="16">
-        <v>0</v>
-      </c>
-      <c r="F6" s="16">
+      <c r="E6" s="15">
+        <v>0</v>
+      </c>
+      <c r="F6" s="15">
         <v>9500</v>
       </c>
     </row>
@@ -4717,13 +4716,13 @@
       <c r="C7" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D7" s="16">
+      <c r="D7" s="15">
         <v>7161.2524999999996</v>
       </c>
-      <c r="E7" s="16">
+      <c r="E7" s="15">
         <v>-0.0001</v>
       </c>
-      <c r="F7" s="16">
+      <c r="F7" s="15">
         <v>7161.2524000000003</v>
       </c>
     </row>
@@ -4737,13 +4736,13 @@
       <c r="C8" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D8" s="16">
+      <c r="D8" s="15">
         <v>-624.65750000000003</v>
       </c>
-      <c r="E8" s="16">
+      <c r="E8" s="15">
         <v>-1714.0900999999999</v>
       </c>
-      <c r="F8" s="16">
+      <c r="F8" s="15">
         <v>-2338.7476000000001</v>
       </c>
     </row>
@@ -4757,13 +4756,13 @@
       <c r="C9" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D9" s="16">
+      <c r="D9" s="15">
         <v>-1714.0899999999999</v>
       </c>
-      <c r="E9" s="16">
+      <c r="E9" s="15">
         <v>1714.0899999999999</v>
       </c>
-      <c r="F9" s="16">
+      <c r="F9" s="15">
         <v>0</v>
       </c>
     </row>
@@ -4777,13 +4776,13 @@
       <c r="C10" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D10" s="16">
-        <v>0</v>
-      </c>
-      <c r="E10" s="16">
+      <c r="D10" s="15">
+        <v>0</v>
+      </c>
+      <c r="E10" s="15">
         <v>9500</v>
       </c>
-      <c r="F10" s="16">
+      <c r="F10" s="15">
         <v>9500</v>
       </c>
     </row>
@@ -4797,13 +4796,13 @@
       <c r="C11" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D11" s="16">
+      <c r="D11" s="15">
         <v>-691.58510000000001</v>
       </c>
-      <c r="E11" s="16">
+      <c r="E11" s="15">
         <v>7161.2524000000003</v>
       </c>
-      <c r="F11" s="16">
+      <c r="F11" s="15">
         <v>6469.6673000000001</v>
       </c>
     </row>
@@ -4817,13 +4816,13 @@
       <c r="C12" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D12" s="16">
+      <c r="D12" s="15">
         <v>-691.58510000000001</v>
       </c>
-      <c r="E12" s="16">
+      <c r="E12" s="15">
         <v>-2338.7476000000001</v>
       </c>
-      <c r="F12" s="16">
+      <c r="F12" s="15">
         <v>-3030.3326999999999</v>
       </c>
     </row>
@@ -4837,13 +4836,13 @@
       <c r="C13" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D13" s="16">
-        <v>0</v>
-      </c>
-      <c r="E13" s="16">
-        <v>0</v>
-      </c>
-      <c r="F13" s="16">
+      <c r="D13" s="15">
+        <v>0</v>
+      </c>
+      <c r="E13" s="15">
+        <v>0</v>
+      </c>
+      <c r="F13" s="15">
         <v>0</v>
       </c>
     </row>
@@ -4857,13 +4856,13 @@
       <c r="C14" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D14" s="16">
-        <v>0</v>
-      </c>
-      <c r="E14" s="16">
+      <c r="D14" s="15">
+        <v>0</v>
+      </c>
+      <c r="E14" s="15">
         <v>9500</v>
       </c>
-      <c r="F14" s="16">
+      <c r="F14" s="15">
         <v>9500</v>
       </c>
     </row>
@@ -4877,13 +4876,13 @@
       <c r="C15" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D15" s="16">
+      <c r="D15" s="15">
         <v>-1554.9032</v>
       </c>
-      <c r="E15" s="16">
+      <c r="E15" s="15">
         <v>6469.6673000000001</v>
       </c>
-      <c r="F15" s="16">
+      <c r="F15" s="15">
         <v>4914.7641000000003</v>
       </c>
     </row>
@@ -4897,13 +4896,13 @@
       <c r="C16" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D16" s="16">
+      <c r="D16" s="15">
         <v>-1554.9032</v>
       </c>
-      <c r="E16" s="16">
+      <c r="E16" s="15">
         <v>-3030.3326999999999</v>
       </c>
-      <c r="F16" s="16">
+      <c r="F16" s="15">
         <v>-4585.2358999999997</v>
       </c>
     </row>
@@ -4917,13 +4916,13 @@
       <c r="C17" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D17" s="16">
-        <v>0</v>
-      </c>
-      <c r="E17" s="16">
-        <v>0</v>
-      </c>
-      <c r="F17" s="16">
+      <c r="D17" s="15">
+        <v>0</v>
+      </c>
+      <c r="E17" s="15">
+        <v>0</v>
+      </c>
+      <c r="F17" s="15">
         <v>0</v>
       </c>
     </row>
@@ -4937,13 +4936,13 @@
       <c r="C18" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D18" s="16">
+      <c r="D18" s="15">
         <v>3000</v>
       </c>
-      <c r="E18" s="16">
+      <c r="E18" s="15">
         <v>9500</v>
       </c>
-      <c r="F18" s="16">
+      <c r="F18" s="15">
         <v>12500</v>
       </c>
     </row>
@@ -4957,13 +4956,13 @@
       <c r="C19" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D19" s="16">
+      <c r="D19" s="15">
         <v>2056.3166000000001</v>
       </c>
-      <c r="E19" s="16">
+      <c r="E19" s="15">
         <v>4914.7641000000003</v>
       </c>
-      <c r="F19" s="16">
+      <c r="F19" s="15">
         <v>6971.0807000000004</v>
       </c>
     </row>
@@ -4977,13 +4976,13 @@
       <c r="C20" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D20" s="16">
+      <c r="D20" s="15">
         <v>-943.68340000000001</v>
       </c>
-      <c r="E20" s="16">
+      <c r="E20" s="15">
         <v>-4585.2358999999997</v>
       </c>
-      <c r="F20" s="16">
+      <c r="F20" s="15">
         <v>-5528.9192999999996</v>
       </c>
     </row>
@@ -4997,13 +4996,13 @@
       <c r="C21" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D21" s="16">
-        <v>0</v>
-      </c>
-      <c r="E21" s="16">
-        <v>0</v>
-      </c>
-      <c r="F21" s="16">
+      <c r="D21" s="15">
+        <v>0</v>
+      </c>
+      <c r="E21" s="15">
+        <v>0</v>
+      </c>
+      <c r="F21" s="15">
         <v>0</v>
       </c>
     </row>
@@ -5029,10 +5028,10 @@
   </cols>
   <sheetData>
     <row r="1" ht="15">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="6" t="s">
         <v>61</v>
       </c>
     </row>
@@ -5397,8 +5396,9 @@
   <cols>
     <col customWidth="1" min="1" max="1" style="1" width="21.7109375"/>
     <col customWidth="1" min="2" max="2" style="1" width="21.85546875"/>
-    <col customWidth="1" min="3" max="3" style="1" width="24.140625"/>
-    <col customWidth="1" min="5" max="5" style="1" width="23.140625"/>
+    <col customWidth="1" min="3" max="3" width="21.85546875"/>
+    <col customWidth="1" min="4" max="4" style="1" width="24.140625"/>
+    <col customWidth="1" min="5" max="5" style="1" width="26.7109375"/>
     <col customWidth="1" min="7" max="7" style="1" width="7"/>
     <col customWidth="1" min="8" max="8" style="1" width="20.42578125"/>
     <col customWidth="1" min="9" max="9" style="1" width="21.140625"/>
@@ -5412,10 +5412,10 @@
   </cols>
   <sheetData>
     <row r="1" ht="14.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>25</v>
       </c>
     </row>
@@ -5427,10 +5427,10 @@
         <v>27</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>63</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>50</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>64</v>
@@ -5480,14 +5480,12 @@
         <v>0</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>77</v>
-      </c>
+      <c r="E3" s="1"/>
       <c r="F3" s="1">
         <v>202201</v>
       </c>
@@ -5518,14 +5516,12 @@
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>77</v>
-      </c>
+      <c r="E4" s="1"/>
       <c r="F4" s="1">
         <v>202201</v>
       </c>
@@ -5571,14 +5567,12 @@
         <v>2</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>77</v>
-      </c>
+      <c r="E5" s="1"/>
       <c r="F5" s="1">
         <v>202201</v>
       </c>
@@ -5624,14 +5618,12 @@
         <v>3</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>77</v>
-      </c>
+      <c r="E6" s="1"/>
       <c r="F6" s="1">
         <v>202201</v>
       </c>
@@ -5677,10 +5669,10 @@
         <v>4</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>77</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>38</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>77</v>
@@ -5727,13 +5719,13 @@
         <v>20220430</v>
       </c>
       <c r="B8" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C8" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>77</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>38</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1">
@@ -5745,228 +5737,89 @@
       <c r="H8" s="1" t="s">
         <v>78</v>
       </c>
+      <c r="I8" s="1">
+        <v>50</v>
+      </c>
       <c r="J8" s="1" t="s">
         <v>79</v>
       </c>
+      <c r="K8" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="L8" s="1">
+        <v>24</v>
+      </c>
+      <c r="M8" s="1">
+        <v>1200</v>
+      </c>
       <c r="N8" s="1" t="s">
-        <v>80</v>
+        <v>88</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>79</v>
       </c>
       <c r="P8" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q8" s="1" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9" ht="12.75" customHeight="1">
-      <c r="A9" s="1">
-        <v>20220430</v>
-      </c>
-      <c r="B9" s="1">
-        <v>1</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>38</v>
-      </c>
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="D9" s="1"/>
       <c r="E9" s="1"/>
-      <c r="F9" s="1">
-        <v>202201</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="I9" s="1">
-        <v>-200</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="L9" s="1">
-        <v>1</v>
-      </c>
-      <c r="M9" s="1">
-        <v>-200</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="O9" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="P9" s="1">
-        <v>1</v>
-      </c>
-      <c r="Q9" s="1" t="s">
-        <v>82</v>
-      </c>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+      <c r="O9" s="1"/>
+      <c r="P9" s="1"/>
+      <c r="Q9" s="1"/>
     </row>
     <row r="10" ht="12.75" customHeight="1">
-      <c r="A10" s="1">
-        <v>20220430</v>
-      </c>
-      <c r="B10" s="1">
-        <v>2</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>38</v>
-      </c>
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="D10" s="1"/>
       <c r="E10" s="1"/>
-      <c r="F10" s="1">
-        <v>202201</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="I10" s="1">
-        <v>100</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="L10" s="1">
-        <v>12</v>
-      </c>
-      <c r="M10" s="1">
-        <v>1200</v>
-      </c>
-      <c r="N10" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="O10" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="P10" s="1">
-        <v>2</v>
-      </c>
-      <c r="Q10" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="1"/>
+      <c r="O10" s="1"/>
+      <c r="P10" s="1"/>
+      <c r="Q10" s="1"/>
     </row>
     <row r="11" ht="12.75" customHeight="1">
-      <c r="A11" s="1">
-        <v>20220430</v>
-      </c>
-      <c r="B11" s="1">
-        <v>3</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>38</v>
-      </c>
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="D11" s="1"/>
       <c r="E11" s="1"/>
-      <c r="F11" s="1">
-        <v>202201</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="I11" s="1">
-        <v>300</v>
-      </c>
-      <c r="J11" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="L11" s="1">
-        <v>1</v>
-      </c>
-      <c r="M11" s="1">
-        <v>300</v>
-      </c>
-      <c r="N11" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="O11" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="P11" s="1">
-        <v>3</v>
-      </c>
-      <c r="Q11" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="12" ht="12.75" customHeight="1">
-      <c r="A12" s="1">
-        <v>20220430</v>
-      </c>
-      <c r="B12" s="1">
-        <v>4</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1">
-        <v>202201</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="I12" s="1">
-        <v>50</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="L12" s="1">
-        <v>24</v>
-      </c>
-      <c r="M12" s="1">
-        <v>1200</v>
-      </c>
-      <c r="N12" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="O12" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="P12" s="1">
-        <v>5</v>
-      </c>
-      <c r="Q12" s="1" t="s">
-        <v>89</v>
-      </c>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+      <c r="O11" s="1"/>
+      <c r="P11" s="1"/>
+      <c r="Q11" s="1"/>
     </row>
   </sheetData>
-  <sortState ref="A3:Q12">
-    <sortCondition ref="A3:A12"/>
-    <sortCondition ref="B3:B12"/>
-    <sortCondition ref="D3:D12"/>
+  <sortState ref="A3:Q8">
+    <sortCondition ref="A3:A8"/>
+    <sortCondition ref="B3:B8"/>
   </sortState>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.78750000000000009" right="0.78750000000000009" top="1.05277777777778" bottom="1.05277777777778" header="0.78750000000000009" footer="0.78750000000000009"/>
@@ -5998,1484 +5851,1484 @@
   </cols>
   <sheetData>
     <row r="1" ht="21">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="2" ht="15">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="E2" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="L2" s="19" t="s">
+      <c r="L2" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="M2" s="20" t="s">
+      <c r="M2" s="19" t="s">
         <v>97</v>
       </c>
-      <c r="N2" s="20" t="s">
+      <c r="N2" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="O2" s="20" t="s">
+      <c r="O2" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="P2" s="20" t="s">
+      <c r="P2" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="Q2" s="20" t="s">
+      <c r="Q2" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="R2" s="20" t="s">
+      <c r="R2" s="19" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="3" ht="15">
-      <c r="A3" s="9">
+      <c r="A3" s="8">
         <v>1</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="E3" s="9">
-        <v>0</v>
-      </c>
-      <c r="L3" s="19"/>
-      <c r="M3" s="9" t="s">
+      <c r="E3" s="8">
+        <v>0</v>
+      </c>
+      <c r="L3" s="18"/>
+      <c r="M3" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="N3" s="21">
-        <v>0</v>
-      </c>
-      <c r="O3" s="22">
+      <c r="N3" s="20">
+        <v>0</v>
+      </c>
+      <c r="O3" s="21">
         <v>44620</v>
       </c>
-      <c r="P3" s="22">
+      <c r="P3" s="21">
         <v>44620</v>
       </c>
-      <c r="Q3" s="23" t="s">
+      <c r="Q3" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="R3" s="23">
+      <c r="R3" s="22">
         <v>1900</v>
       </c>
     </row>
     <row r="4" ht="15">
-      <c r="A4" s="9">
+      <c r="A4" s="8">
         <v>2</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="E4" s="9"/>
-      <c r="L4" s="19"/>
-      <c r="M4" s="9" t="s">
+      <c r="E4" s="8"/>
+      <c r="L4" s="18"/>
+      <c r="M4" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="N4" s="21">
-        <v>0</v>
-      </c>
-      <c r="O4" s="22">
+      <c r="N4" s="20">
+        <v>0</v>
+      </c>
+      <c r="O4" s="21">
         <v>44712</v>
       </c>
-      <c r="P4" s="22">
+      <c r="P4" s="21">
         <v>44712</v>
       </c>
-      <c r="Q4" s="23" t="s">
+      <c r="Q4" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="R4" s="23">
+      <c r="R4" s="22">
         <v>600</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9">
+      <c r="A5" s="8">
         <v>3</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="E5" s="9"/>
+      <c r="E5" s="8"/>
     </row>
     <row r="6">
-      <c r="A6" s="9">
+      <c r="A6" s="8">
         <v>4</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="E6" s="9"/>
+      <c r="E6" s="8"/>
     </row>
     <row r="7">
-      <c r="A7" s="9">
+      <c r="A7" s="8">
         <v>5</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="E7" s="9"/>
+      <c r="E7" s="8"/>
     </row>
     <row r="8">
-      <c r="A8" s="9">
-        <v>0</v>
-      </c>
-      <c r="B8" s="9" t="s">
+      <c r="A8" s="8">
+        <v>0</v>
+      </c>
+      <c r="B8" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
     </row>
     <row r="11" ht="21">
-      <c r="A11" s="24" t="s">
+      <c r="A11" s="23" t="s">
         <v>113</v>
       </c>
-      <c r="B11" s="24"/>
-      <c r="C11" s="24"/>
-      <c r="D11" s="24"/>
-      <c r="E11" s="24"/>
-      <c r="F11" s="24"/>
-      <c r="G11" s="24"/>
-      <c r="H11" s="24"/>
+      <c r="B11" s="23"/>
+      <c r="C11" s="23"/>
+      <c r="D11" s="23"/>
+      <c r="E11" s="23"/>
+      <c r="F11" s="23"/>
+      <c r="G11" s="23"/>
+      <c r="H11" s="23"/>
     </row>
     <row r="12" ht="15">
-      <c r="A12" s="18" t="s">
+      <c r="A12" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="C12" s="18" t="s">
+      <c r="C12" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="D12" s="18" t="s">
+      <c r="D12" s="17" t="s">
         <v>115</v>
       </c>
-      <c r="E12" s="18" t="s">
+      <c r="E12" s="17" t="s">
         <v>116</v>
       </c>
-      <c r="F12" s="18" t="s">
+      <c r="F12" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="G12" s="18" t="s">
+      <c r="G12" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="H12" s="18" t="s">
+      <c r="H12" s="17" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="13" ht="15">
-      <c r="A13" s="9">
+      <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="9" t="str">
+      <c r="B13" s="8" t="str">
         <f t="shared" ref="B13:B16" si="0">IFERROR(VLOOKUP(A13,A3:$B$7,2,FALSE()),"")</f>
         <v>Discount</v>
       </c>
-      <c r="C13" s="25">
+      <c r="C13" s="24">
         <v>-200</v>
       </c>
-      <c r="D13" s="25">
+      <c r="D13" s="24">
         <f t="shared" ref="D13:D16" si="1">IFERROR(IF(VLOOKUP(B13,$B$3:$C$7,2,FALSE())="USE SALES PRICE",C13,VLOOKUP(B13,$B$3:$E$7,4,FALSE())),"")</f>
         <v>0</v>
       </c>
-      <c r="E13" s="25">
+      <c r="E13" s="24">
         <f t="shared" ref="E13:E16" si="2">IFERROR(D13/$D$18,"")</f>
         <v>0</v>
       </c>
-      <c r="F13" s="25">
+      <c r="F13" s="24">
         <f t="shared" ref="F13:F16" si="3">IFERROR(E13*$C$18,"")</f>
         <v>0</v>
       </c>
-      <c r="G13" s="22">
+      <c r="G13" s="21">
         <v>44576</v>
       </c>
-      <c r="H13" s="22">
+      <c r="H13" s="21">
         <v>44576</v>
       </c>
     </row>
     <row r="14" ht="15">
-      <c r="A14" s="9">
+      <c r="A14" s="8">
         <v>2</v>
       </c>
-      <c r="B14" s="9" t="str">
+      <c r="B14" s="8" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">SaaS Basic Subscription</v>
       </c>
-      <c r="C14" s="25">
+      <c r="C14" s="24">
         <v>1200</v>
       </c>
-      <c r="D14" s="25">
+      <c r="D14" s="24">
         <f t="shared" si="1"/>
         <v>1200</v>
       </c>
-      <c r="E14" s="25">
+      <c r="E14" s="24">
         <f t="shared" si="2"/>
         <v>0.5714285714285714</v>
       </c>
-      <c r="F14" s="25">
+      <c r="F14" s="24">
         <f t="shared" si="3"/>
         <v>1085.7142857142856</v>
       </c>
-      <c r="G14" s="22">
+      <c r="G14" s="21">
         <v>44576</v>
       </c>
-      <c r="H14" s="22">
+      <c r="H14" s="21">
         <v>44941</v>
       </c>
     </row>
     <row r="15" ht="15">
-      <c r="A15" s="9">
+      <c r="A15" s="8">
         <v>3</v>
       </c>
-      <c r="B15" s="9" t="str">
+      <c r="B15" s="8" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">SaaS Implementation</v>
       </c>
-      <c r="C15" s="25">
+      <c r="C15" s="24">
         <v>300</v>
       </c>
-      <c r="D15" s="25">
+      <c r="D15" s="24">
         <f t="shared" si="1"/>
         <v>300</v>
       </c>
-      <c r="E15" s="25">
+      <c r="E15" s="24">
         <f t="shared" si="2"/>
         <v>0.14285714285714285</v>
       </c>
-      <c r="F15" s="25">
+      <c r="F15" s="24">
         <f t="shared" si="3"/>
         <v>271.42857142857139</v>
       </c>
-      <c r="G15" s="22">
+      <c r="G15" s="21">
         <v>44576</v>
       </c>
-      <c r="H15" s="22">
+      <c r="H15" s="21">
         <v>44576</v>
       </c>
     </row>
     <row r="16" ht="15">
-      <c r="A16" s="9">
+      <c r="A16" s="8">
         <v>5</v>
       </c>
-      <c r="B16" s="9" t="str">
+      <c r="B16" s="8" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">SaaS Premium Subscription</v>
       </c>
-      <c r="C16" s="25">
+      <c r="C16" s="24">
         <v>600</v>
       </c>
-      <c r="D16" s="25">
+      <c r="D16" s="24">
         <f t="shared" si="1"/>
         <v>600</v>
       </c>
-      <c r="E16" s="25">
+      <c r="E16" s="24">
         <f t="shared" si="2"/>
         <v>0.2857142857142857</v>
       </c>
-      <c r="F16" s="25">
+      <c r="F16" s="24">
         <f t="shared" si="3"/>
         <v>542.85714285714278</v>
       </c>
-      <c r="G16" s="22">
+      <c r="G16" s="21">
         <v>44576</v>
       </c>
-      <c r="H16" s="22">
+      <c r="H16" s="21">
         <v>44941</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="9"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="25"/>
-      <c r="D17" s="25"/>
-      <c r="E17" s="25"/>
-      <c r="F17" s="25"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
+      <c r="A17" s="8"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="24"/>
+      <c r="D17" s="24"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="24"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
     </row>
     <row r="18" ht="15">
-      <c r="A18" s="26" t="s">
+      <c r="A18" s="25" t="s">
         <v>120</v>
       </c>
-      <c r="B18" s="26"/>
-      <c r="C18" s="27">
+      <c r="B18" s="25"/>
+      <c r="C18" s="26">
         <f>SUM(C13:C17)</f>
         <v>1900</v>
       </c>
-      <c r="D18" s="27">
+      <c r="D18" s="26">
         <f>SUM(D13:D17)</f>
         <v>2100</v>
       </c>
-      <c r="E18" s="27">
+      <c r="E18" s="26">
         <f>SUM(E13:E17)</f>
         <v>0.99999999999999989</v>
       </c>
-      <c r="F18" s="27">
+      <c r="F18" s="26">
         <f>SUM(F13:F17)</f>
         <v>1899.9999999999995</v>
       </c>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
     </row>
     <row r="20">
-      <c r="B20" s="28" t="s">
+      <c r="B20" s="27" t="s">
         <v>106</v>
       </c>
-      <c r="C20" s="28"/>
-      <c r="D20" s="28"/>
+      <c r="C20" s="27"/>
+      <c r="D20" s="27"/>
     </row>
     <row r="21">
-      <c r="B21" s="29" t="s">
+      <c r="B21" s="28" t="s">
         <v>121</v>
       </c>
-      <c r="C21" s="29" t="s">
+      <c r="C21" s="28" t="s">
         <v>122</v>
       </c>
-      <c r="D21" s="29" t="s">
+      <c r="D21" s="28" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="30">
+      <c r="B22" s="29">
         <v>44592</v>
       </c>
-      <c r="C22" s="9">
+      <c r="C22" s="8">
         <f t="shared" ref="C22:C34" si="4">-ROUND($F$14/$D$35*D22,4)</f>
         <v>-47.593000000000004</v>
       </c>
-      <c r="D22" s="9">
+      <c r="D22" s="8">
         <f>B22-G14</f>
         <v>16</v>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="30">
+      <c r="B23" s="29">
         <v>44620</v>
       </c>
-      <c r="C23" s="9">
+      <c r="C23" s="8">
         <f t="shared" si="4"/>
         <v>-83.287700000000001</v>
       </c>
-      <c r="D23" s="9">
+      <c r="D23" s="8">
         <f t="shared" ref="D23:D34" si="5">B23-B22</f>
         <v>28</v>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="30">
+      <c r="B24" s="29">
         <v>44651</v>
       </c>
-      <c r="C24" s="9">
+      <c r="C24" s="8">
         <f t="shared" si="4"/>
         <v>-92.211399999999998</v>
       </c>
-      <c r="D24" s="9">
+      <c r="D24" s="8">
         <f t="shared" si="5"/>
         <v>31</v>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="30">
+      <c r="B25" s="29">
         <v>44681</v>
       </c>
-      <c r="C25" s="9">
+      <c r="C25" s="8">
         <f t="shared" si="4"/>
         <v>-89.236800000000002</v>
       </c>
-      <c r="D25" s="9">
+      <c r="D25" s="8">
         <f t="shared" si="5"/>
         <v>30</v>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="30">
+      <c r="B26" s="29">
         <v>44712</v>
       </c>
-      <c r="C26" s="9">
+      <c r="C26" s="8">
         <f t="shared" si="4"/>
         <v>-92.211399999999998</v>
       </c>
-      <c r="D26" s="9">
+      <c r="D26" s="8">
         <f t="shared" si="5"/>
         <v>31</v>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="30">
+      <c r="B27" s="29">
         <v>44742</v>
       </c>
-      <c r="C27" s="9">
+      <c r="C27" s="8">
         <f t="shared" si="4"/>
         <v>-89.236800000000002</v>
       </c>
-      <c r="D27" s="9">
+      <c r="D27" s="8">
         <f t="shared" si="5"/>
         <v>30</v>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="30">
+      <c r="B28" s="29">
         <v>44773</v>
       </c>
-      <c r="C28" s="9">
+      <c r="C28" s="8">
         <f t="shared" si="4"/>
         <v>-92.211399999999998</v>
       </c>
-      <c r="D28" s="9">
+      <c r="D28" s="8">
         <f t="shared" si="5"/>
         <v>31</v>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="30">
+      <c r="B29" s="29">
         <v>44804</v>
       </c>
-      <c r="C29" s="9">
+      <c r="C29" s="8">
         <f t="shared" si="4"/>
         <v>-92.211399999999998</v>
       </c>
-      <c r="D29" s="9">
+      <c r="D29" s="8">
         <f t="shared" si="5"/>
         <v>31</v>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="30">
+      <c r="B30" s="29">
         <v>44834</v>
       </c>
-      <c r="C30" s="9">
+      <c r="C30" s="8">
         <f t="shared" si="4"/>
         <v>-89.236800000000002</v>
       </c>
-      <c r="D30" s="9">
+      <c r="D30" s="8">
         <f t="shared" si="5"/>
         <v>30</v>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="30">
+      <c r="B31" s="29">
         <v>44865</v>
       </c>
-      <c r="C31" s="9">
+      <c r="C31" s="8">
         <f t="shared" si="4"/>
         <v>-92.211399999999998</v>
       </c>
-      <c r="D31" s="9">
+      <c r="D31" s="8">
         <f t="shared" si="5"/>
         <v>31</v>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="30">
+      <c r="B32" s="29">
         <v>44895</v>
       </c>
-      <c r="C32" s="9">
+      <c r="C32" s="8">
         <f t="shared" si="4"/>
         <v>-89.236800000000002</v>
       </c>
-      <c r="D32" s="9">
+      <c r="D32" s="8">
         <f t="shared" si="5"/>
         <v>30</v>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="30">
+      <c r="B33" s="29">
         <v>44926</v>
       </c>
-      <c r="C33" s="9">
+      <c r="C33" s="8">
         <f t="shared" si="4"/>
         <v>-92.211399999999998</v>
       </c>
-      <c r="D33" s="9">
+      <c r="D33" s="8">
         <f t="shared" si="5"/>
         <v>31</v>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="30">
+      <c r="B34" s="29">
         <v>44941</v>
       </c>
-      <c r="C34" s="9">
+      <c r="C34" s="8">
         <f t="shared" si="4"/>
         <v>-44.618400000000001</v>
       </c>
-      <c r="D34" s="9">
+      <c r="D34" s="8">
         <f t="shared" si="5"/>
         <v>15</v>
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="9"/>
-      <c r="C35" s="9">
+      <c r="B35" s="8"/>
+      <c r="C35" s="8">
         <f>SUM(C22:C34)</f>
         <v>-1085.7147000000002</v>
       </c>
-      <c r="D35" s="9">
+      <c r="D35" s="8">
         <f>SUM(D22:D34)</f>
         <v>365</v>
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="28" t="s">
+      <c r="B38" s="27" t="s">
         <v>111</v>
       </c>
-      <c r="C38" s="28"/>
-      <c r="D38" s="28"/>
+      <c r="C38" s="27"/>
+      <c r="D38" s="27"/>
     </row>
     <row r="39">
-      <c r="B39" s="29" t="s">
+      <c r="B39" s="28" t="s">
         <v>121</v>
       </c>
-      <c r="C39" s="29" t="s">
+      <c r="C39" s="28" t="s">
         <v>122</v>
       </c>
-      <c r="D39" s="29" t="s">
+      <c r="D39" s="28" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="40">
-      <c r="B40" s="30">
+      <c r="B40" s="29">
         <v>44592</v>
       </c>
-      <c r="C40" s="9">
+      <c r="C40" s="8">
         <f t="shared" ref="C40:C52" si="6">-ROUND($F$16/$D$53*D40,4)</f>
         <v>-23.796500000000002</v>
       </c>
-      <c r="D40" s="9">
+      <c r="D40" s="8">
         <f>B40-G16</f>
         <v>16</v>
       </c>
     </row>
     <row r="41">
-      <c r="B41" s="30">
+      <c r="B41" s="29">
         <v>44620</v>
       </c>
-      <c r="C41" s="9">
+      <c r="C41" s="8">
         <f t="shared" si="6"/>
         <v>-41.643799999999999</v>
       </c>
-      <c r="D41" s="9">
+      <c r="D41" s="8">
         <f t="shared" ref="D41:D52" si="7">B41-B40</f>
         <v>28</v>
       </c>
     </row>
     <row r="42">
-      <c r="B42" s="30">
+      <c r="B42" s="29">
         <v>44651</v>
       </c>
-      <c r="C42" s="9">
+      <c r="C42" s="8">
         <f t="shared" si="6"/>
         <v>-46.105699999999999</v>
       </c>
-      <c r="D42" s="9">
+      <c r="D42" s="8">
         <f t="shared" si="7"/>
         <v>31</v>
       </c>
     </row>
     <row r="43">
-      <c r="B43" s="30">
+      <c r="B43" s="29">
         <v>44681</v>
       </c>
-      <c r="C43" s="9">
+      <c r="C43" s="8">
         <f t="shared" si="6"/>
         <v>-44.618400000000001</v>
       </c>
-      <c r="D43" s="9">
+      <c r="D43" s="8">
         <f t="shared" si="7"/>
         <v>30</v>
       </c>
     </row>
     <row r="44">
-      <c r="B44" s="30">
+      <c r="B44" s="29">
         <v>44712</v>
       </c>
-      <c r="C44" s="9">
+      <c r="C44" s="8">
         <f t="shared" si="6"/>
         <v>-46.105699999999999</v>
       </c>
-      <c r="D44" s="9">
+      <c r="D44" s="8">
         <f t="shared" si="7"/>
         <v>31</v>
       </c>
     </row>
     <row r="45">
-      <c r="B45" s="30">
+      <c r="B45" s="29">
         <v>44742</v>
       </c>
-      <c r="C45" s="9">
+      <c r="C45" s="8">
         <f t="shared" si="6"/>
         <v>-44.618400000000001</v>
       </c>
-      <c r="D45" s="9">
+      <c r="D45" s="8">
         <f t="shared" si="7"/>
         <v>30</v>
       </c>
     </row>
     <row r="46">
-      <c r="B46" s="30">
+      <c r="B46" s="29">
         <v>44773</v>
       </c>
-      <c r="C46" s="9">
+      <c r="C46" s="8">
         <f t="shared" si="6"/>
         <v>-46.105699999999999</v>
       </c>
-      <c r="D46" s="9">
+      <c r="D46" s="8">
         <f t="shared" si="7"/>
         <v>31</v>
       </c>
     </row>
     <row r="47">
-      <c r="B47" s="30">
+      <c r="B47" s="29">
         <v>44804</v>
       </c>
-      <c r="C47" s="9">
+      <c r="C47" s="8">
         <f t="shared" si="6"/>
         <v>-46.105699999999999</v>
       </c>
-      <c r="D47" s="9">
+      <c r="D47" s="8">
         <f t="shared" si="7"/>
         <v>31</v>
       </c>
     </row>
     <row r="48">
-      <c r="B48" s="30">
+      <c r="B48" s="29">
         <v>44834</v>
       </c>
-      <c r="C48" s="9">
+      <c r="C48" s="8">
         <f t="shared" si="6"/>
         <v>-44.618400000000001</v>
       </c>
-      <c r="D48" s="9">
+      <c r="D48" s="8">
         <f t="shared" si="7"/>
         <v>30</v>
       </c>
     </row>
     <row r="49">
-      <c r="B49" s="30">
+      <c r="B49" s="29">
         <v>44865</v>
       </c>
-      <c r="C49" s="9">
+      <c r="C49" s="8">
         <f t="shared" si="6"/>
         <v>-46.105699999999999</v>
       </c>
-      <c r="D49" s="9">
+      <c r="D49" s="8">
         <f t="shared" si="7"/>
         <v>31</v>
       </c>
     </row>
     <row r="50">
-      <c r="B50" s="30">
+      <c r="B50" s="29">
         <v>44895</v>
       </c>
-      <c r="C50" s="9">
+      <c r="C50" s="8">
         <f t="shared" si="6"/>
         <v>-44.618400000000001</v>
       </c>
-      <c r="D50" s="9">
+      <c r="D50" s="8">
         <f t="shared" si="7"/>
         <v>30</v>
       </c>
     </row>
     <row r="51">
-      <c r="B51" s="30">
+      <c r="B51" s="29">
         <v>44926</v>
       </c>
-      <c r="C51" s="9">
+      <c r="C51" s="8">
         <f t="shared" si="6"/>
         <v>-46.105699999999999</v>
       </c>
-      <c r="D51" s="9">
+      <c r="D51" s="8">
         <f t="shared" si="7"/>
         <v>31</v>
       </c>
     </row>
     <row r="52">
-      <c r="B52" s="30">
+      <c r="B52" s="29">
         <v>44941</v>
       </c>
-      <c r="C52" s="9">
+      <c r="C52" s="8">
         <f t="shared" si="6"/>
         <v>-22.309200000000001</v>
       </c>
-      <c r="D52" s="9">
+      <c r="D52" s="8">
         <f t="shared" si="7"/>
         <v>15</v>
       </c>
     </row>
     <row r="53">
-      <c r="B53" s="9"/>
-      <c r="C53" s="9">
+      <c r="B53" s="8"/>
+      <c r="C53" s="8">
         <f>SUM(C40:C52)</f>
         <v>-542.85730000000012</v>
       </c>
-      <c r="D53" s="9">
+      <c r="D53" s="8">
         <f>SUM(D40:D52)</f>
         <v>365</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="31" t="s">
+      <c r="A55" s="30" t="s">
         <v>124</v>
       </c>
-      <c r="B55" s="31"/>
-      <c r="C55" s="31"/>
-      <c r="D55" s="31"/>
-      <c r="E55" s="31"/>
-      <c r="F55" s="31"/>
-      <c r="G55" s="31"/>
-      <c r="H55" s="31"/>
-      <c r="I55" s="31"/>
-      <c r="J55" s="31"/>
-      <c r="K55" s="31"/>
-      <c r="L55" s="31"/>
-      <c r="M55" s="31"/>
-      <c r="N55" s="31"/>
-      <c r="O55" s="31"/>
-      <c r="P55" s="31"/>
+      <c r="B55" s="30"/>
+      <c r="C55" s="30"/>
+      <c r="D55" s="30"/>
+      <c r="E55" s="30"/>
+      <c r="F55" s="30"/>
+      <c r="G55" s="30"/>
+      <c r="H55" s="30"/>
+      <c r="I55" s="30"/>
+      <c r="J55" s="30"/>
+      <c r="K55" s="30"/>
+      <c r="L55" s="30"/>
+      <c r="M55" s="30"/>
+      <c r="N55" s="30"/>
+      <c r="O55" s="30"/>
+      <c r="P55" s="30"/>
     </row>
     <row r="57" ht="21">
-      <c r="A57" s="17" t="s">
+      <c r="A57" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="B57" s="17"/>
-      <c r="C57" s="17"/>
-      <c r="D57" s="17"/>
-      <c r="E57" s="17"/>
+      <c r="B57" s="16"/>
+      <c r="C57" s="16"/>
+      <c r="D57" s="16"/>
+      <c r="E57" s="16"/>
     </row>
     <row r="58" ht="15">
-      <c r="A58" s="18" t="s">
+      <c r="A58" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="B58" s="18" t="s">
+      <c r="B58" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="C58" s="18" t="s">
+      <c r="C58" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="D58" s="18" t="s">
+      <c r="D58" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="E58" s="18" t="s">
+      <c r="E58" s="17" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="9">
+      <c r="A59" s="8">
         <v>1</v>
       </c>
-      <c r="B59" s="9" t="s">
+      <c r="B59" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="C59" s="9" t="s">
+      <c r="C59" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="D59" s="9" t="s">
+      <c r="D59" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="E59" s="9">
+      <c r="E59" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="9">
+      <c r="A60" s="8">
         <v>2</v>
       </c>
-      <c r="B60" s="9" t="s">
+      <c r="B60" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="C60" s="9" t="s">
+      <c r="C60" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="D60" s="9" t="s">
+      <c r="D60" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="E60" s="9"/>
+      <c r="E60" s="8"/>
     </row>
     <row r="61">
-      <c r="A61" s="9">
+      <c r="A61" s="8">
         <v>3</v>
       </c>
-      <c r="B61" s="9" t="s">
+      <c r="B61" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="C61" s="9" t="s">
+      <c r="C61" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="D61" s="9" t="s">
+      <c r="D61" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="E61" s="9"/>
+      <c r="E61" s="8"/>
     </row>
     <row r="62">
-      <c r="A62" s="9">
+      <c r="A62" s="8">
         <v>4</v>
       </c>
-      <c r="B62" s="9" t="s">
+      <c r="B62" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="C62" s="9" t="s">
+      <c r="C62" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="D62" s="9" t="s">
+      <c r="D62" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="E62" s="9"/>
+      <c r="E62" s="8"/>
     </row>
     <row r="63">
-      <c r="A63" s="9">
+      <c r="A63" s="8">
         <v>5</v>
       </c>
-      <c r="B63" s="9" t="s">
+      <c r="B63" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="C63" s="9" t="s">
+      <c r="C63" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="D63" s="9" t="s">
+      <c r="D63" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="E63" s="9"/>
+      <c r="E63" s="8"/>
     </row>
     <row r="64">
-      <c r="A64" s="9">
-        <v>0</v>
-      </c>
-      <c r="B64" s="9" t="s">
+      <c r="A64" s="8">
+        <v>0</v>
+      </c>
+      <c r="B64" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="C64" s="9"/>
-      <c r="D64" s="9"/>
-      <c r="E64" s="9"/>
+      <c r="C64" s="8"/>
+      <c r="D64" s="8"/>
+      <c r="E64" s="8"/>
     </row>
     <row r="67" ht="21">
-      <c r="A67" s="24" t="s">
+      <c r="A67" s="23" t="s">
         <v>113</v>
       </c>
-      <c r="B67" s="24"/>
-      <c r="C67" s="24"/>
-      <c r="D67" s="24"/>
-      <c r="E67" s="24"/>
-      <c r="F67" s="24"/>
-      <c r="G67" s="24"/>
-      <c r="H67" s="24"/>
+      <c r="B67" s="23"/>
+      <c r="C67" s="23"/>
+      <c r="D67" s="23"/>
+      <c r="E67" s="23"/>
+      <c r="F67" s="23"/>
+      <c r="G67" s="23"/>
+      <c r="H67" s="23"/>
     </row>
     <row r="68" ht="15">
-      <c r="A68" s="18" t="s">
+      <c r="A68" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="B68" s="18" t="s">
+      <c r="B68" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="C68" s="18" t="s">
+      <c r="C68" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="D68" s="18" t="s">
+      <c r="D68" s="17" t="s">
         <v>115</v>
       </c>
-      <c r="E68" s="18" t="s">
+      <c r="E68" s="17" t="s">
         <v>116</v>
       </c>
-      <c r="F68" s="18" t="s">
+      <c r="F68" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="G68" s="18" t="s">
+      <c r="G68" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="H68" s="18" t="s">
+      <c r="H68" s="17" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="69" ht="15">
-      <c r="A69" s="9">
+      <c r="A69" s="8">
         <v>1</v>
       </c>
-      <c r="B69" s="9" t="str">
+      <c r="B69" s="8" t="str">
         <f t="shared" ref="B69:B72" si="8">IFERROR(VLOOKUP(A69,A$7:$B59,2,FALSE()),"")</f>
         <v>Discount</v>
       </c>
-      <c r="C69" s="25">
+      <c r="C69" s="24">
         <v>-200</v>
       </c>
-      <c r="D69" s="25">
+      <c r="D69" s="24">
         <f t="shared" ref="D69:D72" si="9">IFERROR(IF(VLOOKUP(B69,$B$3:$C$7,2,FALSE())="USE SALES PRICE",C69,VLOOKUP(B69,$B$3:$E$7,4,FALSE())),"")</f>
         <v>0</v>
       </c>
-      <c r="E69" s="25">
+      <c r="E69" s="24">
         <f>IFERROR(D69/$D$18,"")</f>
         <v>0</v>
       </c>
-      <c r="F69" s="25">
+      <c r="F69" s="24">
         <f>IFERROR(E69*$C$18,"")</f>
         <v>0</v>
       </c>
-      <c r="G69" s="22">
+      <c r="G69" s="21">
         <v>44576</v>
       </c>
-      <c r="H69" s="22">
+      <c r="H69" s="21">
         <v>44576</v>
       </c>
     </row>
     <row r="70" ht="15">
-      <c r="A70" s="9">
+      <c r="A70" s="8">
         <v>2</v>
       </c>
-      <c r="B70" s="9" t="str">
+      <c r="B70" s="8" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve">SaaS Basic Subscription</v>
       </c>
-      <c r="C70" s="25">
+      <c r="C70" s="24">
         <v>1200</v>
       </c>
-      <c r="D70" s="25">
+      <c r="D70" s="24">
         <f t="shared" si="9"/>
         <v>1200</v>
       </c>
-      <c r="E70" s="25">
+      <c r="E70" s="24">
         <f t="shared" ref="E70:E72" si="10">IFERROR(D70/$D$74,"")</f>
         <v>0.44444444444444442</v>
       </c>
-      <c r="F70" s="25">
+      <c r="F70" s="24">
         <f t="shared" ref="F70:F72" si="11">IFERROR(E70*$C$74,"")</f>
         <v>1111.1111111111111</v>
       </c>
-      <c r="G70" s="22">
+      <c r="G70" s="21">
         <v>44576</v>
       </c>
-      <c r="H70" s="22">
+      <c r="H70" s="21">
         <v>44941</v>
       </c>
     </row>
     <row r="71" ht="15">
-      <c r="A71" s="9">
+      <c r="A71" s="8">
         <v>3</v>
       </c>
-      <c r="B71" s="9" t="str">
+      <c r="B71" s="8" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve">SaaS Implementation</v>
       </c>
-      <c r="C71" s="25">
+      <c r="C71" s="24">
         <v>300</v>
       </c>
-      <c r="D71" s="25">
+      <c r="D71" s="24">
         <f t="shared" si="9"/>
         <v>300</v>
       </c>
-      <c r="E71" s="25">
+      <c r="E71" s="24">
         <f t="shared" si="10"/>
         <v>0.1111111111111111</v>
       </c>
-      <c r="F71" s="25">
+      <c r="F71" s="24">
         <f t="shared" si="11"/>
         <v>277.77777777777777</v>
       </c>
-      <c r="G71" s="22">
+      <c r="G71" s="21">
         <v>44576</v>
       </c>
-      <c r="H71" s="22">
+      <c r="H71" s="21">
         <v>44576</v>
       </c>
     </row>
     <row r="72" ht="15">
-      <c r="A72" s="9">
+      <c r="A72" s="8">
         <v>5</v>
       </c>
-      <c r="B72" s="9" t="str">
+      <c r="B72" s="8" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve">SaaS Premium Subscription</v>
       </c>
-      <c r="C72" s="25">
+      <c r="C72" s="24">
         <v>1200</v>
       </c>
-      <c r="D72" s="25">
+      <c r="D72" s="24">
         <f t="shared" si="9"/>
         <v>1200</v>
       </c>
-      <c r="E72" s="25">
+      <c r="E72" s="24">
         <f t="shared" si="10"/>
         <v>0.44444444444444442</v>
       </c>
-      <c r="F72" s="25">
+      <c r="F72" s="24">
         <f t="shared" si="11"/>
         <v>1111.1111111111111</v>
       </c>
-      <c r="G72" s="22">
+      <c r="G72" s="21">
         <v>44576</v>
       </c>
-      <c r="H72" s="22">
+      <c r="H72" s="21">
         <v>44941</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="9"/>
-      <c r="B73" s="9"/>
-      <c r="C73" s="25"/>
-      <c r="D73" s="25"/>
-      <c r="E73" s="25"/>
-      <c r="F73" s="25"/>
-      <c r="G73" s="9"/>
-      <c r="H73" s="9"/>
+      <c r="A73" s="8"/>
+      <c r="B73" s="8"/>
+      <c r="C73" s="24"/>
+      <c r="D73" s="24"/>
+      <c r="E73" s="24"/>
+      <c r="F73" s="24"/>
+      <c r="G73" s="8"/>
+      <c r="H73" s="8"/>
     </row>
     <row r="74" ht="15">
-      <c r="A74" s="26" t="s">
+      <c r="A74" s="25" t="s">
         <v>120</v>
       </c>
-      <c r="B74" s="26"/>
-      <c r="C74" s="27">
+      <c r="B74" s="25"/>
+      <c r="C74" s="26">
         <f>SUM(C69:C73)</f>
         <v>2500</v>
       </c>
-      <c r="D74" s="27">
+      <c r="D74" s="26">
         <f>SUM(D69:D73)</f>
         <v>2700</v>
       </c>
-      <c r="E74" s="27">
+      <c r="E74" s="26">
         <f>SUM(E69:E73)</f>
         <v>1</v>
       </c>
-      <c r="F74" s="27">
+      <c r="F74" s="26">
         <f>SUM(F69:F73)</f>
         <v>2500</v>
       </c>
-      <c r="G74" s="9"/>
-      <c r="H74" s="9"/>
+      <c r="G74" s="8"/>
+      <c r="H74" s="8"/>
     </row>
     <row r="76">
-      <c r="B76" s="28" t="s">
+      <c r="B76" s="27" t="s">
         <v>106</v>
       </c>
-      <c r="C76" s="28"/>
-      <c r="D76" s="28"/>
+      <c r="C76" s="27"/>
+      <c r="D76" s="27"/>
     </row>
     <row r="77">
-      <c r="B77" s="29" t="s">
+      <c r="B77" s="28" t="s">
         <v>121</v>
       </c>
-      <c r="C77" s="29" t="s">
+      <c r="C77" s="28" t="s">
         <v>122</v>
       </c>
-      <c r="D77" s="29" t="s">
+      <c r="D77" s="28" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="78">
-      <c r="B78" s="30">
+      <c r="B78" s="29">
         <v>44592</v>
       </c>
-      <c r="C78" s="9">
+      <c r="C78" s="8">
         <f t="shared" ref="C78:C90" si="12">-ROUND($F$70/$D$91*D78,4)</f>
         <v>-48.706200000000003</v>
       </c>
-      <c r="D78" s="9">
+      <c r="D78" s="8">
         <f>B78-G70</f>
         <v>16</v>
       </c>
     </row>
     <row r="79">
-      <c r="B79" s="30">
+      <c r="B79" s="29">
         <v>44620</v>
       </c>
-      <c r="C79" s="9">
+      <c r="C79" s="8">
         <f t="shared" si="12"/>
         <v>-85.235900000000001</v>
       </c>
-      <c r="D79" s="9">
+      <c r="D79" s="8">
         <f t="shared" ref="D79:D90" si="13">B79-B78</f>
         <v>28</v>
       </c>
     </row>
     <row r="80">
-      <c r="B80" s="30">
+      <c r="B80" s="29">
         <v>44651</v>
       </c>
-      <c r="C80" s="9">
+      <c r="C80" s="8">
         <f t="shared" si="12"/>
         <v>-94.368300000000005</v>
       </c>
-      <c r="D80" s="9">
+      <c r="D80" s="8">
         <f t="shared" si="13"/>
         <v>31</v>
       </c>
     </row>
     <row r="81">
-      <c r="B81" s="30">
+      <c r="B81" s="29">
         <v>44681</v>
       </c>
-      <c r="C81" s="9">
+      <c r="C81" s="8">
         <f t="shared" si="12"/>
         <v>-91.324200000000005</v>
       </c>
-      <c r="D81" s="9">
+      <c r="D81" s="8">
         <f t="shared" si="13"/>
         <v>30</v>
       </c>
     </row>
     <row r="82">
-      <c r="B82" s="30">
+      <c r="B82" s="29">
         <v>44712</v>
       </c>
-      <c r="C82" s="9">
+      <c r="C82" s="8">
         <f t="shared" si="12"/>
         <v>-94.368300000000005</v>
       </c>
-      <c r="D82" s="9">
+      <c r="D82" s="8">
         <f t="shared" si="13"/>
         <v>31</v>
       </c>
     </row>
     <row r="83">
-      <c r="B83" s="30">
+      <c r="B83" s="29">
         <v>44742</v>
       </c>
-      <c r="C83" s="9">
+      <c r="C83" s="8">
         <f t="shared" si="12"/>
         <v>-91.324200000000005</v>
       </c>
-      <c r="D83" s="9">
+      <c r="D83" s="8">
         <f t="shared" si="13"/>
         <v>30</v>
       </c>
     </row>
     <row r="84">
-      <c r="B84" s="30">
+      <c r="B84" s="29">
         <v>44773</v>
       </c>
-      <c r="C84" s="9">
+      <c r="C84" s="8">
         <f t="shared" si="12"/>
         <v>-94.368300000000005</v>
       </c>
-      <c r="D84" s="9">
+      <c r="D84" s="8">
         <f t="shared" si="13"/>
         <v>31</v>
       </c>
     </row>
     <row r="85">
-      <c r="B85" s="30">
+      <c r="B85" s="29">
         <v>44804</v>
       </c>
-      <c r="C85" s="9">
+      <c r="C85" s="8">
         <f t="shared" si="12"/>
         <v>-94.368300000000005</v>
       </c>
-      <c r="D85" s="9">
+      <c r="D85" s="8">
         <f t="shared" si="13"/>
         <v>31</v>
       </c>
     </row>
     <row r="86">
-      <c r="B86" s="30">
+      <c r="B86" s="29">
         <v>44834</v>
       </c>
-      <c r="C86" s="9">
+      <c r="C86" s="8">
         <f t="shared" si="12"/>
         <v>-91.324200000000005</v>
       </c>
-      <c r="D86" s="9">
+      <c r="D86" s="8">
         <f t="shared" si="13"/>
         <v>30</v>
       </c>
     </row>
     <row r="87">
-      <c r="B87" s="30">
+      <c r="B87" s="29">
         <v>44865</v>
       </c>
-      <c r="C87" s="9">
+      <c r="C87" s="8">
         <f t="shared" si="12"/>
         <v>-94.368300000000005</v>
       </c>
-      <c r="D87" s="9">
+      <c r="D87" s="8">
         <f t="shared" si="13"/>
         <v>31</v>
       </c>
     </row>
     <row r="88">
-      <c r="B88" s="30">
+      <c r="B88" s="29">
         <v>44895</v>
       </c>
-      <c r="C88" s="9">
+      <c r="C88" s="8">
         <f t="shared" si="12"/>
         <v>-91.324200000000005</v>
       </c>
-      <c r="D88" s="9">
+      <c r="D88" s="8">
         <f t="shared" si="13"/>
         <v>30</v>
       </c>
     </row>
     <row r="89">
-      <c r="B89" s="30">
+      <c r="B89" s="29">
         <v>44926</v>
       </c>
-      <c r="C89" s="9">
+      <c r="C89" s="8">
         <f t="shared" si="12"/>
         <v>-94.368300000000005</v>
       </c>
-      <c r="D89" s="9">
+      <c r="D89" s="8">
         <f t="shared" si="13"/>
         <v>31</v>
       </c>
     </row>
     <row r="90">
-      <c r="B90" s="30">
+      <c r="B90" s="29">
         <v>44941</v>
       </c>
-      <c r="C90" s="9">
+      <c r="C90" s="8">
         <f t="shared" si="12"/>
         <v>-45.662100000000002</v>
       </c>
-      <c r="D90" s="9">
+      <c r="D90" s="8">
         <f t="shared" si="13"/>
         <v>15</v>
       </c>
     </row>
     <row r="91">
-      <c r="B91" s="9"/>
-      <c r="C91" s="9">
+      <c r="B91" s="8"/>
+      <c r="C91" s="8">
         <f>SUM(C78:C90)</f>
         <v>-1111.1108000000002</v>
       </c>
-      <c r="D91" s="9">
+      <c r="D91" s="8">
         <f>SUM(D78:D90)</f>
         <v>365</v>
       </c>
     </row>
     <row r="94">
-      <c r="B94" s="28" t="s">
+      <c r="B94" s="27" t="s">
         <v>111</v>
       </c>
-      <c r="C94" s="28"/>
-      <c r="D94" s="28"/>
+      <c r="C94" s="27"/>
+      <c r="D94" s="27"/>
     </row>
     <row r="95">
-      <c r="B95" s="29" t="s">
+      <c r="B95" s="28" t="s">
         <v>121</v>
       </c>
-      <c r="C95" s="29" t="s">
+      <c r="C95" s="28" t="s">
         <v>122</v>
       </c>
-      <c r="D95" s="29" t="s">
+      <c r="D95" s="28" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="96">
-      <c r="B96" s="30">
+      <c r="B96" s="29">
         <v>44592</v>
       </c>
-      <c r="C96" s="9">
+      <c r="C96" s="8">
         <f t="shared" ref="C96:C108" si="14">-ROUND($F$72/$D$109*D96,4)</f>
         <v>-48.706200000000003</v>
       </c>
-      <c r="D96" s="9">
+      <c r="D96" s="8">
         <f>B96-G72</f>
         <v>16</v>
       </c>
     </row>
     <row r="97">
-      <c r="B97" s="30">
+      <c r="B97" s="29">
         <v>44620</v>
       </c>
-      <c r="C97" s="9">
+      <c r="C97" s="8">
         <f t="shared" si="14"/>
         <v>-85.235900000000001</v>
       </c>
-      <c r="D97" s="9">
+      <c r="D97" s="8">
         <f t="shared" ref="D97:D108" si="15">B97-B96</f>
         <v>28</v>
       </c>
     </row>
     <row r="98">
-      <c r="B98" s="30">
+      <c r="B98" s="29">
         <v>44651</v>
       </c>
-      <c r="C98" s="9">
+      <c r="C98" s="8">
         <f t="shared" si="14"/>
         <v>-94.368300000000005</v>
       </c>
-      <c r="D98" s="9">
+      <c r="D98" s="8">
         <f t="shared" si="15"/>
         <v>31</v>
       </c>
     </row>
     <row r="99">
-      <c r="B99" s="30">
+      <c r="B99" s="29">
         <v>44681</v>
       </c>
-      <c r="C99" s="9">
+      <c r="C99" s="8">
         <f t="shared" si="14"/>
         <v>-91.324200000000005</v>
       </c>
-      <c r="D99" s="9">
+      <c r="D99" s="8">
         <f t="shared" si="15"/>
         <v>30</v>
       </c>
     </row>
     <row r="100">
-      <c r="B100" s="30">
+      <c r="B100" s="29">
         <v>44712</v>
       </c>
-      <c r="C100" s="9">
+      <c r="C100" s="8">
         <f t="shared" si="14"/>
         <v>-94.368300000000005</v>
       </c>
-      <c r="D100" s="9">
+      <c r="D100" s="8">
         <f t="shared" si="15"/>
         <v>31</v>
       </c>
     </row>
     <row r="101">
-      <c r="B101" s="30">
+      <c r="B101" s="29">
         <v>44742</v>
       </c>
-      <c r="C101" s="9">
+      <c r="C101" s="8">
         <f t="shared" si="14"/>
         <v>-91.324200000000005</v>
       </c>
-      <c r="D101" s="9">
+      <c r="D101" s="8">
         <f t="shared" si="15"/>
         <v>30</v>
       </c>
     </row>
     <row r="102">
-      <c r="B102" s="30">
+      <c r="B102" s="29">
         <v>44773</v>
       </c>
-      <c r="C102" s="9">
+      <c r="C102" s="8">
         <f t="shared" si="14"/>
         <v>-94.368300000000005</v>
       </c>
-      <c r="D102" s="9">
+      <c r="D102" s="8">
         <f t="shared" si="15"/>
         <v>31</v>
       </c>
     </row>
     <row r="103">
-      <c r="B103" s="30">
+      <c r="B103" s="29">
         <v>44804</v>
       </c>
-      <c r="C103" s="9">
+      <c r="C103" s="8">
         <f t="shared" si="14"/>
         <v>-94.368300000000005</v>
       </c>
-      <c r="D103" s="9">
+      <c r="D103" s="8">
         <f t="shared" si="15"/>
         <v>31</v>
       </c>
     </row>
     <row r="104">
-      <c r="B104" s="30">
+      <c r="B104" s="29">
         <v>44834</v>
       </c>
-      <c r="C104" s="9">
+      <c r="C104" s="8">
         <f t="shared" si="14"/>
         <v>-91.324200000000005</v>
       </c>
-      <c r="D104" s="9">
+      <c r="D104" s="8">
         <f t="shared" si="15"/>
         <v>30</v>
       </c>
     </row>
     <row r="105">
-      <c r="B105" s="30">
+      <c r="B105" s="29">
         <v>44865</v>
       </c>
-      <c r="C105" s="9">
+      <c r="C105" s="8">
         <f t="shared" si="14"/>
         <v>-94.368300000000005</v>
       </c>
-      <c r="D105" s="9">
+      <c r="D105" s="8">
         <f t="shared" si="15"/>
         <v>31</v>
       </c>
     </row>
     <row r="106">
-      <c r="B106" s="30">
+      <c r="B106" s="29">
         <v>44895</v>
       </c>
-      <c r="C106" s="9">
+      <c r="C106" s="8">
         <f t="shared" si="14"/>
         <v>-91.324200000000005</v>
       </c>
-      <c r="D106" s="9">
+      <c r="D106" s="8">
         <f t="shared" si="15"/>
         <v>30</v>
       </c>
     </row>
     <row r="107">
-      <c r="B107" s="30">
+      <c r="B107" s="29">
         <v>44926</v>
       </c>
-      <c r="C107" s="9">
+      <c r="C107" s="8">
         <f t="shared" si="14"/>
         <v>-94.368300000000005</v>
       </c>
-      <c r="D107" s="9">
+      <c r="D107" s="8">
         <f t="shared" si="15"/>
         <v>31</v>
       </c>
     </row>
     <row r="108">
-      <c r="B108" s="30">
+      <c r="B108" s="29">
         <v>44941</v>
       </c>
-      <c r="C108" s="9">
+      <c r="C108" s="8">
         <f t="shared" si="14"/>
         <v>-45.662100000000002</v>
       </c>
-      <c r="D108" s="9">
+      <c r="D108" s="8">
         <f t="shared" si="15"/>
         <v>15</v>
       </c>
     </row>
     <row r="109">
-      <c r="B109" s="9"/>
-      <c r="C109" s="9">
+      <c r="B109" s="8"/>
+      <c r="C109" s="8">
         <f>SUM(C96:C108)</f>
         <v>-1111.1108000000002</v>
       </c>
-      <c r="D109" s="9">
+      <c r="D109" s="8">
         <f>SUM(D96:D108)</f>
         <v>365</v>
       </c>
@@ -7511,555 +7364,555 @@
   </cols>
   <sheetData>
     <row r="1" ht="14.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="G1" s="7"/>
+      <c r="G1" s="6"/>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="G2" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="I2" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="J2" s="8" t="s">
+      <c r="J2" s="7" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="3" hidden="1">
-      <c r="A3" s="9">
+      <c r="A3" s="8">
         <v>20220131</v>
       </c>
-      <c r="B3" s="9">
-        <v>0</v>
-      </c>
-      <c r="C3" s="9" t="s">
+      <c r="B3" s="8">
+        <v>0</v>
+      </c>
+      <c r="C3" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E3" s="9">
+      <c r="E3" s="8">
         <v>20220131</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="F3" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="G3" s="10">
+      <c r="G3" s="9">
         <v>342.81800000000004</v>
       </c>
-      <c r="H3" s="9">
+      <c r="H3" s="8">
         <v>202201</v>
       </c>
-      <c r="I3" s="9">
+      <c r="I3" s="8">
         <v>202201</v>
       </c>
-      <c r="J3" s="9">
+      <c r="J3" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="4" hidden="1">
-      <c r="A4" s="9">
+      <c r="A4" s="8">
         <v>20220131</v>
       </c>
-      <c r="B4" s="9">
+      <c r="B4" s="8">
         <v>2</v>
       </c>
-      <c r="C4" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D4" s="9" t="s">
+      <c r="C4" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D4" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E4" s="9">
+      <c r="E4" s="8">
         <v>20220131</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="G4" s="10">
+      <c r="G4" s="9">
         <v>-47.593000000000004</v>
       </c>
-      <c r="H4" s="9">
+      <c r="H4" s="8">
         <v>202201</v>
       </c>
-      <c r="I4" s="9">
+      <c r="I4" s="8">
         <v>202201</v>
       </c>
-      <c r="J4" s="9">
+      <c r="J4" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="5" hidden="1">
-      <c r="A5" s="9">
+      <c r="A5" s="8">
         <v>20220131</v>
       </c>
-      <c r="B5" s="9">
+      <c r="B5" s="8">
         <v>3</v>
       </c>
-      <c r="C5" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D5" s="9" t="s">
+      <c r="C5" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="8">
         <v>20220131</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F5" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="G5" s="10">
+      <c r="G5" s="9">
         <v>-271.42860000000002</v>
       </c>
-      <c r="H5" s="9">
+      <c r="H5" s="8">
         <v>202201</v>
       </c>
-      <c r="I5" s="9">
+      <c r="I5" s="8">
         <v>202201</v>
       </c>
-      <c r="J5" s="9">
+      <c r="J5" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="6" hidden="1">
-      <c r="A6" s="9">
+      <c r="A6" s="8">
         <v>20220131</v>
       </c>
-      <c r="B6" s="9">
+      <c r="B6" s="8">
         <v>4</v>
       </c>
-      <c r="C6" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D6" s="9" t="s">
+      <c r="C6" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E6" s="9">
+      <c r="E6" s="8">
         <v>20220131</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="F6" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="G6" s="10">
+      <c r="G6" s="9">
         <v>-23.796500000000002</v>
       </c>
-      <c r="H6" s="9">
+      <c r="H6" s="8">
         <v>202201</v>
       </c>
-      <c r="I6" s="9">
+      <c r="I6" s="8">
         <v>202201</v>
       </c>
-      <c r="J6" s="9">
+      <c r="J6" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="7" ht="12.75" hidden="1" customHeight="1">
-      <c r="A7" s="9">
+      <c r="A7" s="8">
         <v>20220228</v>
       </c>
-      <c r="B7" s="9">
-        <v>0</v>
-      </c>
-      <c r="C7" s="9" t="s">
+      <c r="B7" s="8">
+        <v>0</v>
+      </c>
+      <c r="C7" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="8">
         <v>20220228</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="F7" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="G7" s="10">
+      <c r="G7" s="9">
         <v>1900</v>
       </c>
-      <c r="H7" s="9">
+      <c r="H7" s="8">
         <v>202202</v>
       </c>
-      <c r="I7" s="9">
+      <c r="I7" s="8">
         <v>202202</v>
       </c>
-      <c r="J7" s="9">
+      <c r="J7" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="8" ht="12.75" hidden="1" customHeight="1">
-      <c r="A8" s="9">
+      <c r="A8" s="8">
         <v>20220228</v>
       </c>
-      <c r="B8" s="9">
-        <v>0</v>
-      </c>
-      <c r="C8" s="9" t="s">
+      <c r="B8" s="8">
+        <v>0</v>
+      </c>
+      <c r="C8" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D8" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E8" s="9">
+      <c r="E8" s="8">
         <v>20220228</v>
       </c>
-      <c r="F8" s="9" t="s">
+      <c r="F8" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="G8" s="10">
+      <c r="G8" s="9">
         <v>-342.81800000000004</v>
       </c>
-      <c r="H8" s="9">
+      <c r="H8" s="8">
         <v>202202</v>
       </c>
-      <c r="I8" s="9">
+      <c r="I8" s="8">
         <v>202202</v>
       </c>
-      <c r="J8" s="9">
+      <c r="J8" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="9" ht="12.75" hidden="1" customHeight="1">
-      <c r="A9" s="9">
+      <c r="A9" s="8">
         <v>20220228</v>
       </c>
-      <c r="B9" s="9">
+      <c r="B9" s="8">
         <v>2</v>
       </c>
-      <c r="C9" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D9" s="9" t="s">
+      <c r="C9" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E9" s="9">
+      <c r="E9" s="8">
         <v>20220228</v>
       </c>
-      <c r="F9" s="9" t="s">
+      <c r="F9" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="G9" s="10">
+      <c r="G9" s="9">
         <v>-83.287599999999998</v>
       </c>
-      <c r="H9" s="9">
+      <c r="H9" s="8">
         <v>202202</v>
       </c>
-      <c r="I9" s="9">
+      <c r="I9" s="8">
         <v>202202</v>
       </c>
-      <c r="J9" s="9">
+      <c r="J9" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="10" ht="12.75" hidden="1" customHeight="1">
-      <c r="A10" s="9">
+      <c r="A10" s="8">
         <v>20220228</v>
       </c>
-      <c r="B10" s="9">
+      <c r="B10" s="8">
         <v>4</v>
       </c>
-      <c r="C10" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D10" s="9" t="s">
+      <c r="C10" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E10" s="9">
+      <c r="E10" s="8">
         <v>20220228</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="F10" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="G10" s="10">
+      <c r="G10" s="9">
         <v>-41.643799999999999</v>
       </c>
-      <c r="H10" s="9">
+      <c r="H10" s="8">
         <v>202202</v>
       </c>
-      <c r="I10" s="9">
+      <c r="I10" s="8">
         <v>202202</v>
       </c>
-      <c r="J10" s="9">
+      <c r="J10" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="11" ht="12.75" customHeight="1">
-      <c r="A11" s="9">
+      <c r="A11" s="8">
         <v>20220331</v>
       </c>
-      <c r="B11" s="9">
+      <c r="B11" s="8">
         <v>2</v>
       </c>
-      <c r="C11" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D11" s="9" t="s">
+      <c r="C11" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E11" s="9">
+      <c r="E11" s="8">
         <v>20220331</v>
       </c>
-      <c r="F11" s="9" t="s">
+      <c r="F11" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="G11" s="10">
+      <c r="G11" s="9">
         <v>-92.211399999999998</v>
       </c>
-      <c r="H11" s="9">
+      <c r="H11" s="8">
         <v>202203</v>
       </c>
-      <c r="I11" s="9">
+      <c r="I11" s="8">
         <v>202203</v>
       </c>
-      <c r="J11" s="9">
+      <c r="J11" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="12" ht="12.75" customHeight="1">
-      <c r="A12" s="9">
+      <c r="A12" s="8">
         <v>20220331</v>
       </c>
-      <c r="B12" s="9">
+      <c r="B12" s="8">
         <v>4</v>
       </c>
-      <c r="C12" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D12" s="9" t="s">
+      <c r="C12" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E12" s="9">
+      <c r="E12" s="8">
         <v>20220331</v>
       </c>
-      <c r="F12" s="9" t="s">
+      <c r="F12" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="G12" s="10">
+      <c r="G12" s="9">
         <v>-46.105699999999999</v>
       </c>
-      <c r="H12" s="9">
+      <c r="H12" s="8">
         <v>202203</v>
       </c>
-      <c r="I12" s="9">
+      <c r="I12" s="8">
         <v>202203</v>
       </c>
-      <c r="J12" s="9">
+      <c r="J12" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="13" ht="12.75" hidden="1" customHeight="1">
-      <c r="A13" s="9">
+      <c r="A13" s="8">
         <v>20220430</v>
       </c>
-      <c r="B13" s="9">
+      <c r="B13" s="8">
         <v>2</v>
       </c>
-      <c r="C13" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D13" s="9" t="s">
+      <c r="C13" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D13" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E13" s="9">
+      <c r="E13" s="8">
         <v>20220430</v>
       </c>
-      <c r="F13" s="9" t="s">
+      <c r="F13" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="G13" s="10">
+      <c r="G13" s="9">
         <v>-96.542699999999996</v>
       </c>
-      <c r="H13" s="9">
+      <c r="H13" s="8">
         <v>202204</v>
       </c>
-      <c r="I13" s="9">
+      <c r="I13" s="8">
         <v>202204</v>
       </c>
-      <c r="J13" s="9">
+      <c r="J13" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="14" ht="12.75" hidden="1" customHeight="1">
-      <c r="A14" s="9">
+      <c r="A14" s="8">
         <v>20220430</v>
       </c>
-      <c r="B14" s="9">
+      <c r="B14" s="8">
         <v>3</v>
       </c>
-      <c r="C14" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D14" s="9" t="s">
+      <c r="C14" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D14" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E14" s="9">
+      <c r="E14" s="8">
         <v>20220430</v>
       </c>
-      <c r="F14" s="9" t="s">
+      <c r="F14" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="G14" s="10">
+      <c r="G14" s="9">
         <v>-6.3491999999999997</v>
       </c>
-      <c r="H14" s="9">
+      <c r="H14" s="8">
         <v>202204</v>
       </c>
-      <c r="I14" s="9">
+      <c r="I14" s="8">
         <v>202204</v>
       </c>
-      <c r="J14" s="9">
+      <c r="J14" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="15" ht="12.75" hidden="1" customHeight="1">
-      <c r="A15" s="9">
+      <c r="A15" s="8">
         <v>20220430</v>
       </c>
-      <c r="B15" s="9">
+      <c r="B15" s="8">
         <v>4</v>
       </c>
-      <c r="C15" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D15" s="9" t="s">
+      <c r="C15" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E15" s="9">
+      <c r="E15" s="8">
         <v>20220430</v>
       </c>
-      <c r="F15" s="9" t="s">
+      <c r="F15" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="G15" s="10">
+      <c r="G15" s="9">
         <v>-208.08869999999999</v>
       </c>
-      <c r="H15" s="9">
+      <c r="H15" s="8">
         <v>202204</v>
       </c>
-      <c r="I15" s="9">
+      <c r="I15" s="8">
         <v>202204</v>
       </c>
-      <c r="J15" s="9">
+      <c r="J15" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="16" ht="12.75" hidden="1" customHeight="1">
-      <c r="A16" s="9">
+      <c r="A16" s="8">
         <v>20220531</v>
       </c>
-      <c r="B16" s="9">
-        <v>0</v>
-      </c>
-      <c r="C16" s="9" t="s">
+      <c r="B16" s="8">
+        <v>0</v>
+      </c>
+      <c r="C16" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="D16" s="9" t="s">
+      <c r="D16" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="E16" s="9">
+      <c r="E16" s="8">
         <v>20220531</v>
       </c>
-      <c r="F16" s="9" t="s">
+      <c r="F16" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="G16" s="11">
+      <c r="G16" s="10">
         <v>600</v>
       </c>
-      <c r="H16" s="9">
+      <c r="H16" s="8">
         <v>202205</v>
       </c>
-      <c r="I16" s="9">
+      <c r="I16" s="8">
         <v>202205</v>
       </c>
-      <c r="J16" s="9">
+      <c r="J16" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="17" ht="12.75" hidden="1" customHeight="1">
-      <c r="A17" s="9">
+      <c r="A17" s="8">
         <v>20220531</v>
       </c>
-      <c r="B17" s="9">
+      <c r="B17" s="8">
         <v>2</v>
       </c>
-      <c r="C17" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D17" s="9" t="s">
+      <c r="C17" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D17" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E17" s="9">
+      <c r="E17" s="8">
         <v>20220531</v>
       </c>
-      <c r="F17" s="9" t="s">
+      <c r="F17" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="G17" s="10">
+      <c r="G17" s="9">
         <v>-94.368300000000005</v>
       </c>
-      <c r="H17" s="9">
+      <c r="H17" s="8">
         <v>202205</v>
       </c>
-      <c r="I17" s="9">
+      <c r="I17" s="8">
         <v>202205</v>
       </c>
-      <c r="J17" s="9">
+      <c r="J17" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="18" ht="12.75" hidden="1" customHeight="1">
-      <c r="A18" s="9">
+      <c r="A18" s="8">
         <v>20220531</v>
       </c>
-      <c r="B18" s="9">
+      <c r="B18" s="8">
         <v>4</v>
       </c>
-      <c r="C18" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D18" s="9" t="s">
+      <c r="C18" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D18" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E18" s="9">
+      <c r="E18" s="8">
         <v>20220531</v>
       </c>
-      <c r="F18" s="9" t="s">
+      <c r="F18" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="G18" s="10">
+      <c r="G18" s="9">
         <v>-94.368300000000005</v>
       </c>
-      <c r="H18" s="9">
+      <c r="H18" s="8">
         <v>202205</v>
       </c>
-      <c r="I18" s="9">
+      <c r="I18" s="8">
         <v>202205</v>
       </c>
-      <c r="J18" s="9">
+      <c r="J18" s="8">
         <v>0</v>
       </c>
     </row>
@@ -8097,555 +7950,555 @@
   </cols>
   <sheetData>
     <row r="1" ht="15">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="G1" s="7"/>
+      <c r="G1" s="6"/>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="G2" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="I2" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="J2" s="8" t="s">
+      <c r="J2" s="7" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9">
+      <c r="A3" s="8">
         <v>20220131</v>
       </c>
-      <c r="B3" s="9">
-        <v>0</v>
-      </c>
-      <c r="C3" s="9" t="s">
+      <c r="B3" s="8">
+        <v>0</v>
+      </c>
+      <c r="C3" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E3" s="9">
+      <c r="E3" s="8">
         <v>20220131</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="F3" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="G3" s="10">
+      <c r="G3" s="9">
         <v>685.63599999999997</v>
       </c>
-      <c r="H3" s="9">
+      <c r="H3" s="8">
         <v>202201</v>
       </c>
-      <c r="I3" s="9">
+      <c r="I3" s="8">
         <v>202201</v>
       </c>
-      <c r="J3" s="9">
+      <c r="J3" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9">
+      <c r="A4" s="8">
         <v>20220131</v>
       </c>
-      <c r="B4" s="9">
+      <c r="B4" s="8">
         <v>2</v>
       </c>
-      <c r="C4" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D4" s="9" t="s">
+      <c r="C4" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D4" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E4" s="9">
+      <c r="E4" s="8">
         <v>20220131</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="G4" s="10">
+      <c r="G4" s="9">
         <v>-95.185900000000004</v>
       </c>
-      <c r="H4" s="9">
+      <c r="H4" s="8">
         <v>202201</v>
       </c>
-      <c r="I4" s="9">
+      <c r="I4" s="8">
         <v>202201</v>
       </c>
-      <c r="J4" s="9">
+      <c r="J4" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9">
+      <c r="A5" s="8">
         <v>20220131</v>
       </c>
-      <c r="B5" s="9">
+      <c r="B5" s="8">
         <v>3</v>
       </c>
-      <c r="C5" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D5" s="9" t="s">
+      <c r="C5" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="8">
         <v>20220131</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F5" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="G5" s="10">
+      <c r="G5" s="9">
         <v>-542.85709999999995</v>
       </c>
-      <c r="H5" s="9">
+      <c r="H5" s="8">
         <v>202201</v>
       </c>
-      <c r="I5" s="9">
+      <c r="I5" s="8">
         <v>202201</v>
       </c>
-      <c r="J5" s="9">
+      <c r="J5" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="6" ht="12.75" customHeight="1">
-      <c r="A6" s="9">
+      <c r="A6" s="8">
         <v>20220131</v>
       </c>
-      <c r="B6" s="9">
+      <c r="B6" s="8">
         <v>4</v>
       </c>
-      <c r="C6" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D6" s="9" t="s">
+      <c r="C6" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E6" s="9">
+      <c r="E6" s="8">
         <v>20220131</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="F6" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="G6" s="10">
+      <c r="G6" s="9">
         <v>-47.593000000000004</v>
       </c>
-      <c r="H6" s="9">
+      <c r="H6" s="8">
         <v>202201</v>
       </c>
-      <c r="I6" s="9">
+      <c r="I6" s="8">
         <v>202201</v>
       </c>
-      <c r="J6" s="9">
+      <c r="J6" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="7" ht="12.75" customHeight="1">
-      <c r="A7" s="9">
+      <c r="A7" s="8">
         <v>20220228</v>
       </c>
-      <c r="B7" s="9">
-        <v>0</v>
-      </c>
-      <c r="C7" s="9" t="s">
+      <c r="B7" s="8">
+        <v>0</v>
+      </c>
+      <c r="C7" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="8">
         <v>20220228</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="F7" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="G7" s="10">
+      <c r="G7" s="9">
         <v>3800</v>
       </c>
-      <c r="H7" s="9">
+      <c r="H7" s="8">
         <v>202202</v>
       </c>
-      <c r="I7" s="9">
+      <c r="I7" s="8">
         <v>202202</v>
       </c>
-      <c r="J7" s="9">
+      <c r="J7" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="8" ht="12.75" customHeight="1">
-      <c r="A8" s="9">
+      <c r="A8" s="8">
         <v>20220228</v>
       </c>
-      <c r="B8" s="9">
-        <v>0</v>
-      </c>
-      <c r="C8" s="9" t="s">
+      <c r="B8" s="8">
+        <v>0</v>
+      </c>
+      <c r="C8" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D8" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E8" s="9">
+      <c r="E8" s="8">
         <v>20220228</v>
       </c>
-      <c r="F8" s="9" t="s">
+      <c r="F8" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="G8" s="10">
+      <c r="G8" s="9">
         <v>-685.63599999999997</v>
       </c>
-      <c r="H8" s="9">
+      <c r="H8" s="8">
         <v>202202</v>
       </c>
-      <c r="I8" s="9">
+      <c r="I8" s="8">
         <v>202202</v>
       </c>
-      <c r="J8" s="9">
+      <c r="J8" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="9" ht="12.75" customHeight="1">
-      <c r="A9" s="9">
+      <c r="A9" s="8">
         <v>20220228</v>
       </c>
-      <c r="B9" s="9">
+      <c r="B9" s="8">
         <v>2</v>
       </c>
-      <c r="C9" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D9" s="9" t="s">
+      <c r="C9" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E9" s="9">
+      <c r="E9" s="8">
         <v>20220228</v>
       </c>
-      <c r="F9" s="9" t="s">
+      <c r="F9" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="G9" s="10">
+      <c r="G9" s="9">
         <v>-166.5754</v>
       </c>
-      <c r="H9" s="9">
+      <c r="H9" s="8">
         <v>202202</v>
       </c>
-      <c r="I9" s="9">
+      <c r="I9" s="8">
         <v>202202</v>
       </c>
-      <c r="J9" s="9">
+      <c r="J9" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="10" ht="12.75" customHeight="1">
-      <c r="A10" s="9">
+      <c r="A10" s="8">
         <v>20220228</v>
       </c>
-      <c r="B10" s="9">
+      <c r="B10" s="8">
         <v>4</v>
       </c>
-      <c r="C10" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D10" s="9" t="s">
+      <c r="C10" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E10" s="9">
+      <c r="E10" s="8">
         <v>20220228</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="F10" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="G10" s="10">
+      <c r="G10" s="9">
         <v>-83.287599999999998</v>
       </c>
-      <c r="H10" s="9">
+      <c r="H10" s="8">
         <v>202202</v>
       </c>
-      <c r="I10" s="9">
+      <c r="I10" s="8">
         <v>202202</v>
       </c>
-      <c r="J10" s="9">
+      <c r="J10" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="11" ht="12.75" customHeight="1">
-      <c r="A11" s="9">
+      <c r="A11" s="8">
         <v>20220331</v>
       </c>
-      <c r="B11" s="9">
+      <c r="B11" s="8">
         <v>2</v>
       </c>
-      <c r="C11" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D11" s="9" t="s">
+      <c r="C11" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E11" s="9">
+      <c r="E11" s="8">
         <v>20220331</v>
       </c>
-      <c r="F11" s="9" t="s">
+      <c r="F11" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="G11" s="10">
+      <c r="G11" s="9">
         <v>-184.42269999999999</v>
       </c>
-      <c r="H11" s="9">
+      <c r="H11" s="8">
         <v>202203</v>
       </c>
-      <c r="I11" s="9">
+      <c r="I11" s="8">
         <v>202203</v>
       </c>
-      <c r="J11" s="9">
+      <c r="J11" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="12" ht="12.75" customHeight="1">
-      <c r="A12" s="9">
+      <c r="A12" s="8">
         <v>20220331</v>
       </c>
-      <c r="B12" s="9">
+      <c r="B12" s="8">
         <v>4</v>
       </c>
-      <c r="C12" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D12" s="9" t="s">
+      <c r="C12" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E12" s="9">
+      <c r="E12" s="8">
         <v>20220331</v>
       </c>
-      <c r="F12" s="9" t="s">
+      <c r="F12" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="G12" s="10">
+      <c r="G12" s="9">
         <v>-92.211399999999998</v>
       </c>
-      <c r="H12" s="9">
+      <c r="H12" s="8">
         <v>202203</v>
       </c>
-      <c r="I12" s="9">
+      <c r="I12" s="8">
         <v>202203</v>
       </c>
-      <c r="J12" s="9">
+      <c r="J12" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="13" ht="12.75" customHeight="1">
-      <c r="A13" s="9">
+      <c r="A13" s="8">
         <v>20220430</v>
       </c>
-      <c r="B13" s="9">
+      <c r="B13" s="8">
         <v>2</v>
       </c>
-      <c r="C13" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D13" s="9" t="s">
+      <c r="C13" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D13" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E13" s="9">
+      <c r="E13" s="8">
         <v>20220430</v>
       </c>
-      <c r="F13" s="9" t="s">
+      <c r="F13" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="G13" s="10">
+      <c r="G13" s="9">
         <v>-193.08539999999999</v>
       </c>
-      <c r="H13" s="9">
+      <c r="H13" s="8">
         <v>202204</v>
       </c>
-      <c r="I13" s="9">
+      <c r="I13" s="8">
         <v>202204</v>
       </c>
-      <c r="J13" s="9">
+      <c r="J13" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="14" ht="12.75" customHeight="1">
-      <c r="A14" s="9">
+      <c r="A14" s="8">
         <v>20220430</v>
       </c>
-      <c r="B14" s="9">
+      <c r="B14" s="8">
         <v>3</v>
       </c>
-      <c r="C14" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D14" s="9" t="s">
+      <c r="C14" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D14" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E14" s="9">
+      <c r="E14" s="8">
         <v>20220430</v>
       </c>
-      <c r="F14" s="9" t="s">
+      <c r="F14" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="G14" s="10">
+      <c r="G14" s="9">
         <v>-12.698499999999999</v>
       </c>
-      <c r="H14" s="9">
+      <c r="H14" s="8">
         <v>202204</v>
       </c>
-      <c r="I14" s="9">
+      <c r="I14" s="8">
         <v>202204</v>
       </c>
-      <c r="J14" s="9">
+      <c r="J14" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="15" ht="12.75" customHeight="1">
-      <c r="A15" s="9">
+      <c r="A15" s="8">
         <v>20220430</v>
       </c>
-      <c r="B15" s="9">
+      <c r="B15" s="8">
         <v>4</v>
       </c>
-      <c r="C15" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D15" s="9" t="s">
+      <c r="C15" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E15" s="9">
+      <c r="E15" s="8">
         <v>20220430</v>
       </c>
-      <c r="F15" s="9" t="s">
+      <c r="F15" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="G15" s="10">
+      <c r="G15" s="9">
         <v>-416.17739999999998</v>
       </c>
-      <c r="H15" s="9">
+      <c r="H15" s="8">
         <v>202204</v>
       </c>
-      <c r="I15" s="9">
+      <c r="I15" s="8">
         <v>202204</v>
       </c>
-      <c r="J15" s="9">
+      <c r="J15" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="16" ht="12.75" customHeight="1">
-      <c r="A16" s="9">
+      <c r="A16" s="8">
         <v>20220531</v>
       </c>
-      <c r="B16" s="9">
-        <v>0</v>
-      </c>
-      <c r="C16" s="9" t="s">
+      <c r="B16" s="8">
+        <v>0</v>
+      </c>
+      <c r="C16" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="D16" s="9" t="s">
+      <c r="D16" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="E16" s="9">
+      <c r="E16" s="8">
         <v>20220531</v>
       </c>
-      <c r="F16" s="9" t="s">
+      <c r="F16" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="G16" s="11">
+      <c r="G16" s="10">
         <v>1200</v>
       </c>
-      <c r="H16" s="9">
+      <c r="H16" s="8">
         <v>202205</v>
       </c>
-      <c r="I16" s="9">
+      <c r="I16" s="8">
         <v>202205</v>
       </c>
-      <c r="J16" s="9">
+      <c r="J16" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="17" ht="12.75" customHeight="1">
-      <c r="A17" s="9">
+      <c r="A17" s="8">
         <v>20220531</v>
       </c>
-      <c r="B17" s="9">
+      <c r="B17" s="8">
         <v>2</v>
       </c>
-      <c r="C17" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D17" s="9" t="s">
+      <c r="C17" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D17" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E17" s="9">
+      <c r="E17" s="8">
         <v>20220531</v>
       </c>
-      <c r="F17" s="9" t="s">
+      <c r="F17" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="G17" s="10">
+      <c r="G17" s="9">
         <v>-188.73670000000001</v>
       </c>
-      <c r="H17" s="9">
+      <c r="H17" s="8">
         <v>202205</v>
       </c>
-      <c r="I17" s="9">
+      <c r="I17" s="8">
         <v>202205</v>
       </c>
-      <c r="J17" s="9">
+      <c r="J17" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="18" ht="12.75" customHeight="1">
-      <c r="A18" s="9">
+      <c r="A18" s="8">
         <v>20220531</v>
       </c>
-      <c r="B18" s="9">
+      <c r="B18" s="8">
         <v>4</v>
       </c>
-      <c r="C18" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D18" s="9" t="s">
+      <c r="C18" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D18" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E18" s="9">
+      <c r="E18" s="8">
         <v>20220531</v>
       </c>
-      <c r="F18" s="9" t="s">
+      <c r="F18" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="G18" s="10">
+      <c r="G18" s="9">
         <v>-188.73670000000001</v>
       </c>
-      <c r="H18" s="9">
+      <c r="H18" s="8">
         <v>202205</v>
       </c>
-      <c r="I18" s="9">
+      <c r="I18" s="8">
         <v>202205</v>
       </c>
-      <c r="J18" s="9">
+      <c r="J18" s="8">
         <v>0</v>
       </c>
     </row>
@@ -8669,555 +8522,555 @@
   </cols>
   <sheetData>
     <row r="1" ht="15">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="G1" s="7"/>
+      <c r="G1" s="6"/>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="G2" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="I2" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="J2" s="8" t="s">
+      <c r="J2" s="7" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12">
+      <c r="A3" s="11">
         <v>20220131</v>
       </c>
-      <c r="B3" s="12">
-        <v>0</v>
-      </c>
-      <c r="C3" s="12" t="s">
+      <c r="B3" s="11">
+        <v>0</v>
+      </c>
+      <c r="C3" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="E3" s="12">
+      <c r="E3" s="11">
         <v>20220131</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="F3" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="G3" s="13">
+      <c r="G3" s="12">
         <v>1028.454</v>
       </c>
-      <c r="H3" s="12">
+      <c r="H3" s="11">
         <v>202201</v>
       </c>
-      <c r="I3" s="12">
+      <c r="I3" s="11">
         <v>202201</v>
       </c>
-      <c r="J3" s="12">
+      <c r="J3" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12">
+      <c r="A4" s="11">
         <v>20220131</v>
       </c>
-      <c r="B4" s="12">
+      <c r="B4" s="11">
         <v>2</v>
       </c>
-      <c r="C4" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="D4" s="12" t="s">
+      <c r="C4" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="D4" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="E4" s="12">
+      <c r="E4" s="11">
         <v>20220131</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="F4" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="G4" s="13">
+      <c r="G4" s="12">
         <v>-142.77889999999999</v>
       </c>
-      <c r="H4" s="12">
+      <c r="H4" s="11">
         <v>202201</v>
       </c>
-      <c r="I4" s="12">
+      <c r="I4" s="11">
         <v>202201</v>
       </c>
-      <c r="J4" s="12">
+      <c r="J4" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="12">
+      <c r="A5" s="11">
         <v>20220131</v>
       </c>
-      <c r="B5" s="12">
+      <c r="B5" s="11">
         <v>3</v>
       </c>
-      <c r="C5" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="D5" s="12" t="s">
+      <c r="C5" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="11">
         <v>20220131</v>
       </c>
-      <c r="F5" s="12" t="s">
+      <c r="F5" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="G5" s="13">
+      <c r="G5" s="12">
         <v>-814.28570000000002</v>
       </c>
-      <c r="H5" s="12">
+      <c r="H5" s="11">
         <v>202201</v>
       </c>
-      <c r="I5" s="12">
+      <c r="I5" s="11">
         <v>202201</v>
       </c>
-      <c r="J5" s="12">
+      <c r="J5" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="6" ht="12.75" customHeight="1">
-      <c r="A6" s="12">
+      <c r="A6" s="11">
         <v>20220131</v>
       </c>
-      <c r="B6" s="12">
+      <c r="B6" s="11">
         <v>4</v>
       </c>
-      <c r="C6" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="D6" s="12" t="s">
+      <c r="C6" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="E6" s="12">
+      <c r="E6" s="11">
         <v>20220131</v>
       </c>
-      <c r="F6" s="12" t="s">
+      <c r="F6" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="G6" s="13">
+      <c r="G6" s="12">
         <v>-71.389399999999995</v>
       </c>
-      <c r="H6" s="12">
+      <c r="H6" s="11">
         <v>202201</v>
       </c>
-      <c r="I6" s="12">
+      <c r="I6" s="11">
         <v>202201</v>
       </c>
-      <c r="J6" s="12">
+      <c r="J6" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="7" ht="12.75" customHeight="1">
-      <c r="A7" s="12">
+      <c r="A7" s="11">
         <v>20220228</v>
       </c>
-      <c r="B7" s="12">
-        <v>0</v>
-      </c>
-      <c r="C7" s="12" t="s">
+      <c r="B7" s="11">
+        <v>0</v>
+      </c>
+      <c r="C7" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="E7" s="12">
+      <c r="E7" s="11">
         <v>20220228</v>
       </c>
-      <c r="F7" s="12" t="s">
+      <c r="F7" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="G7" s="13">
+      <c r="G7" s="12">
         <v>5700</v>
       </c>
-      <c r="H7" s="12">
+      <c r="H7" s="11">
         <v>202202</v>
       </c>
-      <c r="I7" s="12">
+      <c r="I7" s="11">
         <v>202202</v>
       </c>
-      <c r="J7" s="12">
+      <c r="J7" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="8" ht="12.75" customHeight="1">
-      <c r="A8" s="12">
+      <c r="A8" s="11">
         <v>20220228</v>
       </c>
-      <c r="B8" s="12">
-        <v>0</v>
-      </c>
-      <c r="C8" s="12" t="s">
+      <c r="B8" s="11">
+        <v>0</v>
+      </c>
+      <c r="C8" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="11">
         <v>20220228</v>
       </c>
-      <c r="F8" s="12" t="s">
+      <c r="F8" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="G8" s="13">
+      <c r="G8" s="12">
         <v>-1028.454</v>
       </c>
-      <c r="H8" s="12">
+      <c r="H8" s="11">
         <v>202202</v>
       </c>
-      <c r="I8" s="12">
+      <c r="I8" s="11">
         <v>202202</v>
       </c>
-      <c r="J8" s="12">
+      <c r="J8" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="9" ht="12.75" customHeight="1">
-      <c r="A9" s="12">
+      <c r="A9" s="11">
         <v>20220228</v>
       </c>
-      <c r="B9" s="12">
+      <c r="B9" s="11">
         <v>2</v>
       </c>
-      <c r="C9" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="D9" s="12" t="s">
+      <c r="C9" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="E9" s="12">
+      <c r="E9" s="11">
         <v>20220228</v>
       </c>
-      <c r="F9" s="12" t="s">
+      <c r="F9" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="G9" s="13">
+      <c r="G9" s="12">
         <v>-249.863</v>
       </c>
-      <c r="H9" s="12">
+      <c r="H9" s="11">
         <v>202202</v>
       </c>
-      <c r="I9" s="12">
+      <c r="I9" s="11">
         <v>202202</v>
       </c>
-      <c r="J9" s="12">
+      <c r="J9" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="10" ht="12.75" customHeight="1">
-      <c r="A10" s="12">
+      <c r="A10" s="11">
         <v>20220228</v>
       </c>
-      <c r="B10" s="12">
+      <c r="B10" s="11">
         <v>4</v>
       </c>
-      <c r="C10" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="D10" s="12" t="s">
+      <c r="C10" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="E10" s="12">
+      <c r="E10" s="11">
         <v>20220228</v>
       </c>
-      <c r="F10" s="12" t="s">
+      <c r="F10" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="G10" s="13">
+      <c r="G10" s="12">
         <v>-124.9315</v>
       </c>
-      <c r="H10" s="12">
+      <c r="H10" s="11">
         <v>202202</v>
       </c>
-      <c r="I10" s="12">
+      <c r="I10" s="11">
         <v>202202</v>
       </c>
-      <c r="J10" s="12">
+      <c r="J10" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="11" ht="12.75" customHeight="1">
-      <c r="A11" s="12">
+      <c r="A11" s="11">
         <v>20220331</v>
       </c>
-      <c r="B11" s="12">
+      <c r="B11" s="11">
         <v>2</v>
       </c>
-      <c r="C11" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="D11" s="12" t="s">
+      <c r="C11" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="E11" s="12">
+      <c r="E11" s="11">
         <v>20220331</v>
       </c>
-      <c r="F11" s="12" t="s">
+      <c r="F11" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="G11" s="13">
+      <c r="G11" s="12">
         <v>-276.63400000000001</v>
       </c>
-      <c r="H11" s="12">
+      <c r="H11" s="11">
         <v>202203</v>
       </c>
-      <c r="I11" s="12">
+      <c r="I11" s="11">
         <v>202203</v>
       </c>
-      <c r="J11" s="12">
+      <c r="J11" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="12" ht="12.75" customHeight="1">
-      <c r="A12" s="12">
+      <c r="A12" s="11">
         <v>20220331</v>
       </c>
-      <c r="B12" s="12">
+      <c r="B12" s="11">
         <v>4</v>
       </c>
-      <c r="C12" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="D12" s="12" t="s">
+      <c r="C12" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="E12" s="12">
+      <c r="E12" s="11">
         <v>20220331</v>
       </c>
-      <c r="F12" s="12" t="s">
+      <c r="F12" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="G12" s="13">
+      <c r="G12" s="12">
         <v>-138.31710000000001</v>
       </c>
-      <c r="H12" s="12">
+      <c r="H12" s="11">
         <v>202203</v>
       </c>
-      <c r="I12" s="12">
+      <c r="I12" s="11">
         <v>202203</v>
       </c>
-      <c r="J12" s="12">
+      <c r="J12" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="13" ht="12.75" customHeight="1">
-      <c r="A13" s="12">
+      <c r="A13" s="11">
         <v>20220430</v>
       </c>
-      <c r="B13" s="12">
+      <c r="B13" s="11">
         <v>2</v>
       </c>
-      <c r="C13" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="D13" s="12" t="s">
+      <c r="C13" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="D13" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="E13" s="12">
+      <c r="E13" s="11">
         <v>20220430</v>
       </c>
-      <c r="F13" s="12" t="s">
+      <c r="F13" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="G13" s="13">
+      <c r="G13" s="12">
         <v>-289.62819999999999</v>
       </c>
-      <c r="H13" s="12">
+      <c r="H13" s="11">
         <v>202204</v>
       </c>
-      <c r="I13" s="12">
+      <c r="I13" s="11">
         <v>202204</v>
       </c>
-      <c r="J13" s="12">
+      <c r="J13" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="14" ht="12.75" customHeight="1">
-      <c r="A14" s="12">
+      <c r="A14" s="11">
         <v>20220430</v>
       </c>
-      <c r="B14" s="12">
+      <c r="B14" s="11">
         <v>3</v>
       </c>
-      <c r="C14" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="D14" s="12" t="s">
+      <c r="C14" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="D14" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="E14" s="12">
+      <c r="E14" s="11">
         <v>20220430</v>
       </c>
-      <c r="F14" s="12" t="s">
+      <c r="F14" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="G14" s="13">
+      <c r="G14" s="12">
         <v>-19.047599999999999</v>
       </c>
-      <c r="H14" s="12">
+      <c r="H14" s="11">
         <v>202204</v>
       </c>
-      <c r="I14" s="12">
+      <c r="I14" s="11">
         <v>202204</v>
       </c>
-      <c r="J14" s="12">
+      <c r="J14" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="15" ht="12.75" customHeight="1">
-      <c r="A15" s="12">
+      <c r="A15" s="11">
         <v>20220430</v>
       </c>
-      <c r="B15" s="12">
+      <c r="B15" s="11">
         <v>4</v>
       </c>
-      <c r="C15" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="D15" s="12" t="s">
+      <c r="C15" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="E15" s="12">
+      <c r="E15" s="11">
         <v>20220430</v>
       </c>
-      <c r="F15" s="12" t="s">
+      <c r="F15" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="G15" s="13">
+      <c r="G15" s="12">
         <v>-624.26610000000005</v>
       </c>
-      <c r="H15" s="12">
+      <c r="H15" s="11">
         <v>202204</v>
       </c>
-      <c r="I15" s="12">
+      <c r="I15" s="11">
         <v>202204</v>
       </c>
-      <c r="J15" s="12">
+      <c r="J15" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="16" ht="12.75" customHeight="1">
-      <c r="A16" s="12">
+      <c r="A16" s="11">
         <v>20220531</v>
       </c>
-      <c r="B16" s="12">
-        <v>0</v>
-      </c>
-      <c r="C16" s="12" t="s">
+      <c r="B16" s="11">
+        <v>0</v>
+      </c>
+      <c r="C16" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="D16" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="E16" s="12">
+      <c r="E16" s="11">
         <v>20220531</v>
       </c>
-      <c r="F16" s="12" t="s">
+      <c r="F16" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="G16" s="14">
+      <c r="G16" s="13">
         <v>1800</v>
       </c>
-      <c r="H16" s="12">
+      <c r="H16" s="11">
         <v>202205</v>
       </c>
-      <c r="I16" s="12">
+      <c r="I16" s="11">
         <v>202205</v>
       </c>
-      <c r="J16" s="12">
+      <c r="J16" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="17" ht="12.75" customHeight="1">
-      <c r="A17" s="12">
+      <c r="A17" s="11">
         <v>20220531</v>
       </c>
-      <c r="B17" s="12">
+      <c r="B17" s="11">
         <v>2</v>
       </c>
-      <c r="C17" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="D17" s="12" t="s">
+      <c r="C17" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="D17" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="E17" s="12">
+      <c r="E17" s="11">
         <v>20220531</v>
       </c>
-      <c r="F17" s="12" t="s">
+      <c r="F17" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="G17" s="13">
+      <c r="G17" s="12">
         <v>-283.10500000000002</v>
       </c>
-      <c r="H17" s="12">
+      <c r="H17" s="11">
         <v>202205</v>
       </c>
-      <c r="I17" s="12">
+      <c r="I17" s="11">
         <v>202205</v>
       </c>
-      <c r="J17" s="12">
+      <c r="J17" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="18" ht="12.75" customHeight="1">
-      <c r="A18" s="12">
+      <c r="A18" s="11">
         <v>20220531</v>
       </c>
-      <c r="B18" s="12">
+      <c r="B18" s="11">
         <v>4</v>
       </c>
-      <c r="C18" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="D18" s="12" t="s">
+      <c r="C18" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="D18" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="E18" s="12">
+      <c r="E18" s="11">
         <v>20220531</v>
       </c>
-      <c r="F18" s="12" t="s">
+      <c r="F18" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="G18" s="13">
+      <c r="G18" s="12">
         <v>-283.10500000000002</v>
       </c>
-      <c r="H18" s="12">
+      <c r="H18" s="11">
         <v>202205</v>
       </c>
-      <c r="I18" s="12">
+      <c r="I18" s="11">
         <v>202205</v>
       </c>
-      <c r="J18" s="12">
+      <c r="J18" s="11">
         <v>0</v>
       </c>
     </row>
@@ -9241,555 +9094,555 @@
   </cols>
   <sheetData>
     <row r="1" ht="15">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="G1" s="7"/>
+      <c r="G1" s="6"/>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="G2" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="I2" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="J2" s="8" t="s">
+      <c r="J2" s="7" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9">
+      <c r="A3" s="8">
         <v>20220131</v>
       </c>
-      <c r="B3" s="9">
-        <v>0</v>
-      </c>
-      <c r="C3" s="9" t="s">
+      <c r="B3" s="8">
+        <v>0</v>
+      </c>
+      <c r="C3" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E3" s="9">
+      <c r="E3" s="8">
         <v>20220131</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="F3" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="G3" s="10">
+      <c r="G3" s="9">
         <v>1371.2719999999999</v>
       </c>
-      <c r="H3" s="9">
+      <c r="H3" s="8">
         <v>202201</v>
       </c>
-      <c r="I3" s="9">
+      <c r="I3" s="8">
         <v>202201</v>
       </c>
-      <c r="J3" s="9">
+      <c r="J3" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9">
+      <c r="A4" s="8">
         <v>20220131</v>
       </c>
-      <c r="B4" s="9">
+      <c r="B4" s="8">
         <v>2</v>
       </c>
-      <c r="C4" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D4" s="9" t="s">
+      <c r="C4" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D4" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E4" s="9">
+      <c r="E4" s="8">
         <v>20220131</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="G4" s="10">
+      <c r="G4" s="9">
         <v>-190.37180000000001</v>
       </c>
-      <c r="H4" s="9">
+      <c r="H4" s="8">
         <v>202201</v>
       </c>
-      <c r="I4" s="9">
+      <c r="I4" s="8">
         <v>202201</v>
       </c>
-      <c r="J4" s="9">
+      <c r="J4" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9">
+      <c r="A5" s="8">
         <v>20220131</v>
       </c>
-      <c r="B5" s="9">
+      <c r="B5" s="8">
         <v>3</v>
       </c>
-      <c r="C5" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D5" s="9" t="s">
+      <c r="C5" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="8">
         <v>20220131</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F5" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="G5" s="10">
+      <c r="G5" s="9">
         <v>-1085.7143000000001</v>
       </c>
-      <c r="H5" s="9">
+      <c r="H5" s="8">
         <v>202201</v>
       </c>
-      <c r="I5" s="9">
+      <c r="I5" s="8">
         <v>202201</v>
       </c>
-      <c r="J5" s="9">
+      <c r="J5" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="6" ht="12.75" customHeight="1">
-      <c r="A6" s="9">
+      <c r="A6" s="8">
         <v>20220131</v>
       </c>
-      <c r="B6" s="9">
+      <c r="B6" s="8">
         <v>4</v>
       </c>
-      <c r="C6" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D6" s="9" t="s">
+      <c r="C6" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E6" s="9">
+      <c r="E6" s="8">
         <v>20220131</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="F6" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="G6" s="10">
+      <c r="G6" s="9">
         <v>-95.185900000000004</v>
       </c>
-      <c r="H6" s="9">
+      <c r="H6" s="8">
         <v>202201</v>
       </c>
-      <c r="I6" s="9">
+      <c r="I6" s="8">
         <v>202201</v>
       </c>
-      <c r="J6" s="9">
+      <c r="J6" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="7" ht="12.75" customHeight="1">
-      <c r="A7" s="9">
+      <c r="A7" s="8">
         <v>20220228</v>
       </c>
-      <c r="B7" s="9">
-        <v>0</v>
-      </c>
-      <c r="C7" s="9" t="s">
+      <c r="B7" s="8">
+        <v>0</v>
+      </c>
+      <c r="C7" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="8">
         <v>20220228</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="F7" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="G7" s="10">
+      <c r="G7" s="9">
         <v>7600</v>
       </c>
-      <c r="H7" s="9">
+      <c r="H7" s="8">
         <v>202202</v>
       </c>
-      <c r="I7" s="9">
+      <c r="I7" s="8">
         <v>202202</v>
       </c>
-      <c r="J7" s="9">
+      <c r="J7" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="8" ht="12.75" customHeight="1">
-      <c r="A8" s="9">
+      <c r="A8" s="8">
         <v>20220228</v>
       </c>
-      <c r="B8" s="9">
-        <v>0</v>
-      </c>
-      <c r="C8" s="9" t="s">
+      <c r="B8" s="8">
+        <v>0</v>
+      </c>
+      <c r="C8" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D8" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E8" s="9">
+      <c r="E8" s="8">
         <v>20220228</v>
       </c>
-      <c r="F8" s="9" t="s">
+      <c r="F8" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="G8" s="10">
+      <c r="G8" s="9">
         <v>-1371.2719999999999</v>
       </c>
-      <c r="H8" s="9">
+      <c r="H8" s="8">
         <v>202202</v>
       </c>
-      <c r="I8" s="9">
+      <c r="I8" s="8">
         <v>202202</v>
       </c>
-      <c r="J8" s="9">
+      <c r="J8" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="9" ht="12.75" customHeight="1">
-      <c r="A9" s="9">
+      <c r="A9" s="8">
         <v>20220228</v>
       </c>
-      <c r="B9" s="9">
+      <c r="B9" s="8">
         <v>2</v>
       </c>
-      <c r="C9" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D9" s="9" t="s">
+      <c r="C9" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E9" s="9">
+      <c r="E9" s="8">
         <v>20220228</v>
       </c>
-      <c r="F9" s="9" t="s">
+      <c r="F9" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="G9" s="10">
+      <c r="G9" s="9">
         <v>-333.15069999999997</v>
       </c>
-      <c r="H9" s="9">
+      <c r="H9" s="8">
         <v>202202</v>
       </c>
-      <c r="I9" s="9">
+      <c r="I9" s="8">
         <v>202202</v>
       </c>
-      <c r="J9" s="9">
+      <c r="J9" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="10" ht="12.75" customHeight="1">
-      <c r="A10" s="9">
+      <c r="A10" s="8">
         <v>20220228</v>
       </c>
-      <c r="B10" s="9">
+      <c r="B10" s="8">
         <v>4</v>
       </c>
-      <c r="C10" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D10" s="9" t="s">
+      <c r="C10" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E10" s="9">
+      <c r="E10" s="8">
         <v>20220228</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="F10" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="G10" s="10">
+      <c r="G10" s="9">
         <v>-166.5754</v>
       </c>
-      <c r="H10" s="9">
+      <c r="H10" s="8">
         <v>202202</v>
       </c>
-      <c r="I10" s="9">
+      <c r="I10" s="8">
         <v>202202</v>
       </c>
-      <c r="J10" s="9">
+      <c r="J10" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="11" ht="12.75" customHeight="1">
-      <c r="A11" s="9">
+      <c r="A11" s="8">
         <v>20220331</v>
       </c>
-      <c r="B11" s="9">
+      <c r="B11" s="8">
         <v>2</v>
       </c>
-      <c r="C11" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D11" s="9" t="s">
+      <c r="C11" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E11" s="9">
+      <c r="E11" s="8">
         <v>20220331</v>
       </c>
-      <c r="F11" s="9" t="s">
+      <c r="F11" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="G11" s="10">
+      <c r="G11" s="9">
         <v>-368.84539999999998</v>
       </c>
-      <c r="H11" s="9">
+      <c r="H11" s="8">
         <v>202203</v>
       </c>
-      <c r="I11" s="9">
+      <c r="I11" s="8">
         <v>202203</v>
       </c>
-      <c r="J11" s="9">
+      <c r="J11" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="12" ht="12.75" customHeight="1">
-      <c r="A12" s="9">
+      <c r="A12" s="8">
         <v>20220331</v>
       </c>
-      <c r="B12" s="9">
+      <c r="B12" s="8">
         <v>4</v>
       </c>
-      <c r="C12" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D12" s="9" t="s">
+      <c r="C12" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E12" s="9">
+      <c r="E12" s="8">
         <v>20220331</v>
       </c>
-      <c r="F12" s="9" t="s">
+      <c r="F12" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="G12" s="10">
+      <c r="G12" s="9">
         <v>-184.42269999999999</v>
       </c>
-      <c r="H12" s="9">
+      <c r="H12" s="8">
         <v>202203</v>
       </c>
-      <c r="I12" s="9">
+      <c r="I12" s="8">
         <v>202203</v>
       </c>
-      <c r="J12" s="9">
+      <c r="J12" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="13" ht="12.75" customHeight="1">
-      <c r="A13" s="9">
+      <c r="A13" s="8">
         <v>20220430</v>
       </c>
-      <c r="B13" s="9">
+      <c r="B13" s="8">
         <v>2</v>
       </c>
-      <c r="C13" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D13" s="9" t="s">
+      <c r="C13" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D13" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E13" s="9">
+      <c r="E13" s="8">
         <v>20220430</v>
       </c>
-      <c r="F13" s="9" t="s">
+      <c r="F13" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="G13" s="10">
+      <c r="G13" s="9">
         <v>-386.17090000000002</v>
       </c>
-      <c r="H13" s="9">
+      <c r="H13" s="8">
         <v>202204</v>
       </c>
-      <c r="I13" s="9">
+      <c r="I13" s="8">
         <v>202204</v>
       </c>
-      <c r="J13" s="9">
+      <c r="J13" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="14" ht="12.75" customHeight="1">
-      <c r="A14" s="9">
+      <c r="A14" s="8">
         <v>20220430</v>
       </c>
-      <c r="B14" s="9">
+      <c r="B14" s="8">
         <v>3</v>
       </c>
-      <c r="C14" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D14" s="9" t="s">
+      <c r="C14" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D14" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E14" s="9">
+      <c r="E14" s="8">
         <v>20220430</v>
       </c>
-      <c r="F14" s="9" t="s">
+      <c r="F14" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="G14" s="10">
+      <c r="G14" s="9">
         <v>-25.396799999999999</v>
       </c>
-      <c r="H14" s="9">
+      <c r="H14" s="8">
         <v>202204</v>
       </c>
-      <c r="I14" s="9">
+      <c r="I14" s="8">
         <v>202204</v>
       </c>
-      <c r="J14" s="9">
+      <c r="J14" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="15" ht="12.75" customHeight="1">
-      <c r="A15" s="9">
+      <c r="A15" s="8">
         <v>20220430</v>
       </c>
-      <c r="B15" s="9">
+      <c r="B15" s="8">
         <v>4</v>
       </c>
-      <c r="C15" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D15" s="9" t="s">
+      <c r="C15" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E15" s="9">
+      <c r="E15" s="8">
         <v>20220430</v>
       </c>
-      <c r="F15" s="9" t="s">
+      <c r="F15" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="G15" s="10">
+      <c r="G15" s="9">
         <v>-832.35479999999995</v>
       </c>
-      <c r="H15" s="9">
+      <c r="H15" s="8">
         <v>202204</v>
       </c>
-      <c r="I15" s="9">
+      <c r="I15" s="8">
         <v>202204</v>
       </c>
-      <c r="J15" s="9">
+      <c r="J15" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="16" ht="12.75" customHeight="1">
-      <c r="A16" s="9">
+      <c r="A16" s="8">
         <v>20220531</v>
       </c>
-      <c r="B16" s="9">
-        <v>0</v>
-      </c>
-      <c r="C16" s="9" t="s">
+      <c r="B16" s="8">
+        <v>0</v>
+      </c>
+      <c r="C16" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="D16" s="9" t="s">
+      <c r="D16" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="E16" s="9">
+      <c r="E16" s="8">
         <v>20220531</v>
       </c>
-      <c r="F16" s="9" t="s">
+      <c r="F16" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="G16" s="11">
+      <c r="G16" s="10">
         <v>2400</v>
       </c>
-      <c r="H16" s="9">
+      <c r="H16" s="8">
         <v>202205</v>
       </c>
-      <c r="I16" s="9">
+      <c r="I16" s="8">
         <v>202205</v>
       </c>
-      <c r="J16" s="9">
+      <c r="J16" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="17" ht="12.75" customHeight="1">
-      <c r="A17" s="9">
+      <c r="A17" s="8">
         <v>20220531</v>
       </c>
-      <c r="B17" s="9">
+      <c r="B17" s="8">
         <v>2</v>
       </c>
-      <c r="C17" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D17" s="9" t="s">
+      <c r="C17" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D17" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E17" s="9">
+      <c r="E17" s="8">
         <v>20220531</v>
       </c>
-      <c r="F17" s="9" t="s">
+      <c r="F17" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="G17" s="10">
+      <c r="G17" s="9">
         <v>-377.47340000000003</v>
       </c>
-      <c r="H17" s="9">
+      <c r="H17" s="8">
         <v>202205</v>
       </c>
-      <c r="I17" s="9">
+      <c r="I17" s="8">
         <v>202205</v>
       </c>
-      <c r="J17" s="9">
+      <c r="J17" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="18" ht="12.75" customHeight="1">
-      <c r="A18" s="9">
+      <c r="A18" s="8">
         <v>20220531</v>
       </c>
-      <c r="B18" s="9">
+      <c r="B18" s="8">
         <v>4</v>
       </c>
-      <c r="C18" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D18" s="9" t="s">
+      <c r="C18" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D18" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E18" s="9">
+      <c r="E18" s="8">
         <v>20220531</v>
       </c>
-      <c r="F18" s="9" t="s">
+      <c r="F18" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="G18" s="10">
+      <c r="G18" s="9">
         <v>-377.47340000000003</v>
       </c>
-      <c r="H18" s="9">
+      <c r="H18" s="8">
         <v>202205</v>
       </c>
-      <c r="I18" s="9">
+      <c r="I18" s="8">
         <v>202205</v>
       </c>
-      <c r="J18" s="9">
+      <c r="J18" s="8">
         <v>0</v>
       </c>
     </row>
@@ -9818,10 +9671,10 @@
   </cols>
   <sheetData>
     <row r="1" ht="15">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>25</v>
       </c>
     </row>
@@ -9864,7 +9717,7 @@
       <c r="E3" s="1">
         <v>0</v>
       </c>
-      <c r="F3" s="15">
+      <c r="F3" s="14">
         <v>342.81800000000004</v>
       </c>
       <c r="G3" s="1">
@@ -9887,7 +9740,7 @@
       <c r="E4" s="1">
         <v>0</v>
       </c>
-      <c r="F4" s="15">
+      <c r="F4" s="14">
         <v>342.81800000000004</v>
       </c>
       <c r="G4" s="1">
@@ -9910,7 +9763,7 @@
       <c r="E5" s="1">
         <v>0</v>
       </c>
-      <c r="F5" s="15">
+      <c r="F5" s="14">
         <v>-47.593000000000004</v>
       </c>
       <c r="G5" s="1">
@@ -9956,7 +9809,7 @@
       <c r="E7" s="1">
         <v>0</v>
       </c>
-      <c r="F7" s="15">
+      <c r="F7" s="14">
         <v>-271.42860000000002</v>
       </c>
       <c r="G7" s="1">
@@ -9979,7 +9832,7 @@
       <c r="E8" s="1">
         <v>0</v>
       </c>
-      <c r="F8" s="15">
+      <c r="F8" s="14">
         <v>-271.42860000000002</v>
       </c>
       <c r="G8" s="1">
@@ -10002,7 +9855,7 @@
       <c r="E9" s="1">
         <v>0</v>
       </c>
-      <c r="F9" s="15">
+      <c r="F9" s="14">
         <v>-23.796500000000002</v>
       </c>
       <c r="G9" s="1">
@@ -10025,7 +9878,7 @@
       <c r="E10" s="1">
         <v>0</v>
       </c>
-      <c r="F10" s="15">
+      <c r="F10" s="14">
         <v>-23.796500000000002</v>
       </c>
       <c r="G10" s="1">
@@ -10048,7 +9901,7 @@
       <c r="E11" s="1">
         <v>0</v>
       </c>
-      <c r="F11" s="15">
+      <c r="F11" s="14">
         <v>1900</v>
       </c>
       <c r="G11" s="1">
@@ -10891,10 +10744,10 @@
   </cols>
   <sheetData>
     <row r="1" ht="15">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>42</v>
       </c>
     </row>
@@ -10937,7 +10790,7 @@
       <c r="E3" s="1">
         <v>0</v>
       </c>
-      <c r="F3" s="15">
+      <c r="F3" s="14">
         <v>685.63599999999997</v>
       </c>
       <c r="G3" s="1">
@@ -10960,7 +10813,7 @@
       <c r="E4" s="1">
         <v>0</v>
       </c>
-      <c r="F4" s="15">
+      <c r="F4" s="14">
         <v>685.63599999999997</v>
       </c>
       <c r="G4" s="1">
@@ -10983,7 +10836,7 @@
       <c r="E5" s="1">
         <v>0</v>
       </c>
-      <c r="F5" s="15">
+      <c r="F5" s="14">
         <v>-95.185900000000004</v>
       </c>
       <c r="G5" s="1">
@@ -11029,7 +10882,7 @@
       <c r="E7" s="1">
         <v>0</v>
       </c>
-      <c r="F7" s="15">
+      <c r="F7" s="14">
         <v>-542.85709999999995</v>
       </c>
       <c r="G7" s="1">
@@ -11052,7 +10905,7 @@
       <c r="E8" s="1">
         <v>0</v>
       </c>
-      <c r="F8" s="15">
+      <c r="F8" s="14">
         <v>-542.85709999999995</v>
       </c>
       <c r="G8" s="1">
@@ -11075,7 +10928,7 @@
       <c r="E9" s="1">
         <v>0</v>
       </c>
-      <c r="F9" s="15">
+      <c r="F9" s="14">
         <v>-47.593000000000004</v>
       </c>
       <c r="G9" s="1">
@@ -11098,7 +10951,7 @@
       <c r="E10" s="1">
         <v>0</v>
       </c>
-      <c r="F10" s="15">
+      <c r="F10" s="14">
         <v>-47.593000000000004</v>
       </c>
       <c r="G10" s="1">
@@ -11121,7 +10974,7 @@
       <c r="E11" s="1">
         <v>0</v>
       </c>
-      <c r="F11" s="15">
+      <c r="F11" s="14">
         <v>3800</v>
       </c>
       <c r="G11" s="1">
@@ -11958,10 +11811,10 @@
   </cols>
   <sheetData>
     <row r="1" ht="15">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>44</v>
       </c>
     </row>
@@ -12004,7 +11857,7 @@
       <c r="E3" s="1">
         <v>0</v>
       </c>
-      <c r="F3" s="15">
+      <c r="F3" s="14">
         <v>1028.454</v>
       </c>
       <c r="G3" s="1">
@@ -12027,7 +11880,7 @@
       <c r="E4" s="1">
         <v>0</v>
       </c>
-      <c r="F4" s="15">
+      <c r="F4" s="14">
         <v>1028.454</v>
       </c>
       <c r="G4" s="1">
@@ -12050,7 +11903,7 @@
       <c r="E5" s="1">
         <v>0</v>
       </c>
-      <c r="F5" s="15">
+      <c r="F5" s="14">
         <v>-142.77889999999999</v>
       </c>
       <c r="G5" s="1">
@@ -12096,7 +11949,7 @@
       <c r="E7" s="1">
         <v>0</v>
       </c>
-      <c r="F7" s="15">
+      <c r="F7" s="14">
         <v>-814.28570000000002</v>
       </c>
       <c r="G7" s="1">
@@ -12119,7 +11972,7 @@
       <c r="E8" s="1">
         <v>0</v>
       </c>
-      <c r="F8" s="15">
+      <c r="F8" s="14">
         <v>-814.28570000000002</v>
       </c>
       <c r="G8" s="1">
@@ -12142,7 +11995,7 @@
       <c r="E9" s="1">
         <v>0</v>
       </c>
-      <c r="F9" s="15">
+      <c r="F9" s="14">
         <v>-71.389399999999995</v>
       </c>
       <c r="G9" s="1">
@@ -12165,7 +12018,7 @@
       <c r="E10" s="1">
         <v>0</v>
       </c>
-      <c r="F10" s="15">
+      <c r="F10" s="14">
         <v>-71.389399999999995</v>
       </c>
       <c r="G10" s="1">
@@ -12188,7 +12041,7 @@
       <c r="E11" s="1">
         <v>0</v>
       </c>
-      <c r="F11" s="15">
+      <c r="F11" s="14">
         <v>5700</v>
       </c>
       <c r="G11" s="1">
@@ -13025,10 +12878,10 @@
   </cols>
   <sheetData>
     <row r="1" ht="15">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>46</v>
       </c>
     </row>
@@ -13071,7 +12924,7 @@
       <c r="E3" s="1">
         <v>0</v>
       </c>
-      <c r="F3" s="15">
+      <c r="F3" s="14">
         <v>1371.2719999999999</v>
       </c>
       <c r="G3" s="1">
@@ -13094,7 +12947,7 @@
       <c r="E4" s="1">
         <v>0</v>
       </c>
-      <c r="F4" s="15">
+      <c r="F4" s="14">
         <v>1371.2719999999999</v>
       </c>
       <c r="G4" s="1">
@@ -13117,7 +12970,7 @@
       <c r="E5" s="1">
         <v>0</v>
       </c>
-      <c r="F5" s="15">
+      <c r="F5" s="14">
         <v>-190.37180000000001</v>
       </c>
       <c r="G5" s="1">
@@ -13163,7 +13016,7 @@
       <c r="E7" s="1">
         <v>0</v>
       </c>
-      <c r="F7" s="15">
+      <c r="F7" s="14">
         <v>-1085.7143000000001</v>
       </c>
       <c r="G7" s="1">
@@ -13186,7 +13039,7 @@
       <c r="E8" s="1">
         <v>0</v>
       </c>
-      <c r="F8" s="15">
+      <c r="F8" s="14">
         <v>-1085.7143000000001</v>
       </c>
       <c r="G8" s="1">
@@ -13209,7 +13062,7 @@
       <c r="E9" s="1">
         <v>0</v>
       </c>
-      <c r="F9" s="15">
+      <c r="F9" s="14">
         <v>-95.185900000000004</v>
       </c>
       <c r="G9" s="1">
@@ -13232,7 +13085,7 @@
       <c r="E10" s="1">
         <v>0</v>
       </c>
-      <c r="F10" s="15">
+      <c r="F10" s="14">
         <v>-95.185900000000004</v>
       </c>
       <c r="G10" s="1">
@@ -13255,7 +13108,7 @@
       <c r="E11" s="1">
         <v>0</v>
       </c>
-      <c r="F11" s="15">
+      <c r="F11" s="14">
         <v>7600</v>
       </c>
       <c r="G11" s="1">
